--- a/translators/translator_cola.xlsx
+++ b/translators/translator_cola.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="Translations Library" sheetId="1" state="visible" r:id="rId3"/>
@@ -49,7 +49,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4142" uniqueCount="2753">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4143" uniqueCount="2754">
   <si>
     <t xml:space="preserve">Sheet name in your format</t>
   </si>
@@ -5629,6 +5629,9 @@
   </si>
   <si>
     <t xml:space="preserve">Nepal</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Netherlands</t>
   </si>
   <si>
     <t xml:space="preserve">nld</t>
@@ -9675,10 +9678,10 @@
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
-        <v>1848</v>
+        <v>1849</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>1849</v>
+        <v>1850</v>
       </c>
       <c r="D2" s="19"/>
       <c r="E2" s="3"/>
@@ -9686,10 +9689,10 @@
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5"/>
       <c r="B3" s="6" t="s">
-        <v>1850</v>
+        <v>1851</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>1851</v>
+        <v>1852</v>
       </c>
       <c r="D3" s="19"/>
       <c r="E3" s="3"/>
@@ -9697,10 +9700,10 @@
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5"/>
       <c r="B4" s="6" t="s">
-        <v>1852</v>
+        <v>1853</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>1853</v>
+        <v>1854</v>
       </c>
       <c r="D4" s="19"/>
       <c r="E4" s="3"/>
@@ -9708,10 +9711,10 @@
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5"/>
       <c r="B5" s="6" t="s">
-        <v>1854</v>
+        <v>1855</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>1855</v>
+        <v>1856</v>
       </c>
       <c r="D5" s="19"/>
       <c r="E5" s="3"/>
@@ -9719,10 +9722,10 @@
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
       <c r="B6" s="6" t="s">
-        <v>1856</v>
+        <v>1857</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1857</v>
+        <v>1858</v>
       </c>
       <c r="D6" s="19"/>
       <c r="E6" s="3"/>
@@ -9730,10 +9733,10 @@
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
       <c r="B7" s="6" t="s">
-        <v>1858</v>
+        <v>1859</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>1859</v>
+        <v>1860</v>
       </c>
       <c r="D7" s="19"/>
       <c r="E7" s="3"/>
@@ -9744,7 +9747,7 @@
         <v>84</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>1860</v>
+        <v>1861</v>
       </c>
       <c r="D8" s="19"/>
       <c r="E8" s="3"/>
@@ -9752,10 +9755,10 @@
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5"/>
       <c r="B9" s="6" t="s">
-        <v>1861</v>
+        <v>1862</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>1862</v>
+        <v>1863</v>
       </c>
       <c r="D9" s="19"/>
       <c r="E9" s="3"/>
@@ -9763,10 +9766,10 @@
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5"/>
       <c r="B10" s="11" t="s">
-        <v>1863</v>
+        <v>1864</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>1864</v>
+        <v>1865</v>
       </c>
       <c r="D10" s="19"/>
       <c r="E10" s="3"/>
@@ -9817,10 +9820,10 @@
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
-        <v>1865</v>
+        <v>1866</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>1866</v>
+        <v>1867</v>
       </c>
       <c r="D2" s="19"/>
       <c r="E2" s="3"/>
@@ -9828,10 +9831,10 @@
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5"/>
       <c r="B3" s="6" t="s">
-        <v>1867</v>
+        <v>1868</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>1868</v>
+        <v>1869</v>
       </c>
       <c r="D3" s="19"/>
       <c r="E3" s="3"/>
@@ -9839,10 +9842,10 @@
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5"/>
       <c r="B4" s="6" t="s">
-        <v>1869</v>
+        <v>1870</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>1870</v>
+        <v>1871</v>
       </c>
       <c r="D4" s="19"/>
       <c r="E4" s="3"/>
@@ -9850,10 +9853,10 @@
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5"/>
       <c r="B5" s="6" t="s">
-        <v>1871</v>
+        <v>1872</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>1872</v>
+        <v>1873</v>
       </c>
       <c r="D5" s="19"/>
       <c r="E5" s="3"/>
@@ -9861,10 +9864,10 @@
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
       <c r="B6" s="6" t="s">
-        <v>1873</v>
+        <v>1874</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1874</v>
+        <v>1875</v>
       </c>
       <c r="D6" s="19"/>
       <c r="E6" s="3"/>
@@ -9872,10 +9875,10 @@
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
       <c r="B7" s="6" t="s">
-        <v>1875</v>
+        <v>1876</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>1876</v>
+        <v>1877</v>
       </c>
       <c r="D7" s="19"/>
       <c r="E7" s="3"/>
@@ -9883,10 +9886,10 @@
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5"/>
       <c r="B8" s="6" t="s">
-        <v>1877</v>
+        <v>1878</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>1878</v>
+        <v>1879</v>
       </c>
       <c r="D8" s="19"/>
       <c r="E8" s="3"/>
@@ -9894,10 +9897,10 @@
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5"/>
       <c r="B9" s="6" t="s">
-        <v>1879</v>
+        <v>1880</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>1880</v>
+        <v>1881</v>
       </c>
       <c r="D9" s="19"/>
       <c r="E9" s="3"/>
@@ -9905,10 +9908,10 @@
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5"/>
       <c r="B10" s="11" t="s">
-        <v>1881</v>
+        <v>1882</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>1882</v>
+        <v>1883</v>
       </c>
       <c r="D10" s="19"/>
       <c r="E10" s="3"/>
@@ -9959,78 +9962,78 @@
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
-        <v>1883</v>
+        <v>1884</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>1884</v>
+        <v>1885</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>1885</v>
+        <v>1886</v>
       </c>
       <c r="E2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5"/>
       <c r="B3" s="6" t="s">
-        <v>1886</v>
+        <v>1887</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>1887</v>
+        <v>1888</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>1888</v>
+        <v>1889</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5"/>
       <c r="B4" s="6" t="s">
-        <v>1889</v>
+        <v>1890</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>1890</v>
+        <v>1891</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>1891</v>
+        <v>1892</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5"/>
       <c r="B5" s="6" t="s">
-        <v>1892</v>
+        <v>1893</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>1894</v>
+        <v>1895</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
       <c r="B6" s="6" t="s">
-        <v>1895</v>
+        <v>1896</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1896</v>
+        <v>1897</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>1897</v>
+        <v>1898</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
       <c r="B7" s="6" t="s">
-        <v>1898</v>
+        <v>1899</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>1899</v>
+        <v>1900</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>1900</v>
+        <v>1901</v>
       </c>
       <c r="E7" s="3"/>
     </row>
@@ -10101,10 +10104,10 @@
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
-        <v>1901</v>
+        <v>1902</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>1902</v>
+        <v>1903</v>
       </c>
       <c r="D2" s="19"/>
       <c r="E2" s="3"/>
@@ -10112,23 +10115,23 @@
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5"/>
       <c r="B3" s="6" t="s">
-        <v>1903</v>
+        <v>1904</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>1904</v>
+        <v>1905</v>
       </c>
       <c r="D3" s="19"/>
       <c r="E3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="14" t="s">
-        <v>1905</v>
+        <v>1906</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>1906</v>
+        <v>1907</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>1907</v>
+        <v>1908</v>
       </c>
       <c r="D4" s="19"/>
       <c r="E4" s="3"/>
@@ -10136,10 +10139,10 @@
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5"/>
       <c r="B5" s="6" t="s">
-        <v>1908</v>
+        <v>1909</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>1909</v>
+        <v>1910</v>
       </c>
       <c r="D5" s="19"/>
       <c r="E5" s="3"/>
@@ -10147,10 +10150,10 @@
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
       <c r="B6" s="6" t="s">
-        <v>1910</v>
+        <v>1911</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1911</v>
+        <v>1912</v>
       </c>
       <c r="D6" s="19"/>
       <c r="E6" s="3"/>
@@ -10158,10 +10161,10 @@
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
       <c r="B7" s="6" t="s">
-        <v>1912</v>
+        <v>1913</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>1913</v>
+        <v>1914</v>
       </c>
       <c r="D7" s="19"/>
       <c r="E7" s="3"/>
@@ -10169,10 +10172,10 @@
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5"/>
       <c r="B8" s="6" t="s">
-        <v>1914</v>
+        <v>1915</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>1915</v>
+        <v>1916</v>
       </c>
       <c r="D8" s="19"/>
       <c r="E8" s="3"/>
@@ -10180,10 +10183,10 @@
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5"/>
       <c r="B9" s="6" t="s">
-        <v>1916</v>
+        <v>1917</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>1917</v>
+        <v>1918</v>
       </c>
       <c r="D9" s="19"/>
       <c r="E9" s="3"/>
@@ -10191,10 +10194,10 @@
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5"/>
       <c r="B10" s="11" t="s">
-        <v>1918</v>
+        <v>1919</v>
       </c>
       <c r="C10" s="12" t="s">
-        <v>1919</v>
+        <v>1920</v>
       </c>
       <c r="D10" s="19"/>
       <c r="E10" s="3"/>
@@ -10245,182 +10248,182 @@
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
-        <v>1920</v>
+        <v>1921</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>1921</v>
+        <v>1922</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>1922</v>
+        <v>1923</v>
       </c>
       <c r="E2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5"/>
       <c r="B3" s="6" t="s">
-        <v>1923</v>
+        <v>1924</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>1924</v>
+        <v>1925</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>1925</v>
+        <v>1926</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5"/>
       <c r="B4" s="6" t="s">
-        <v>1926</v>
+        <v>1927</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>1927</v>
+        <v>1928</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>1928</v>
+        <v>1929</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5"/>
       <c r="B5" s="6" t="s">
-        <v>1929</v>
+        <v>1930</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>1930</v>
+        <v>1931</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>1931</v>
+        <v>1932</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
       <c r="B6" s="6" t="s">
-        <v>1932</v>
+        <v>1933</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1933</v>
+        <v>1934</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>1934</v>
+        <v>1935</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
       <c r="B7" s="6" t="s">
-        <v>1935</v>
+        <v>1936</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>1936</v>
+        <v>1937</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>1937</v>
+        <v>1938</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5"/>
       <c r="B8" s="6" t="s">
-        <v>1938</v>
+        <v>1939</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>1939</v>
+        <v>1940</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>1940</v>
+        <v>1941</v>
       </c>
       <c r="E8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5"/>
       <c r="B9" s="6" t="s">
-        <v>1941</v>
+        <v>1942</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>1942</v>
+        <v>1943</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>1943</v>
+        <v>1944</v>
       </c>
       <c r="E9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5"/>
       <c r="B10" s="6" t="s">
-        <v>1944</v>
+        <v>1945</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>1945</v>
+        <v>1946</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>1946</v>
+        <v>1947</v>
       </c>
       <c r="E10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
       <c r="B11" s="6" t="s">
-        <v>1947</v>
+        <v>1948</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>1948</v>
+        <v>1949</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>1949</v>
+        <v>1950</v>
       </c>
       <c r="E11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5"/>
       <c r="B12" s="6" t="s">
-        <v>1950</v>
+        <v>1951</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>1951</v>
+        <v>1952</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>1952</v>
+        <v>1953</v>
       </c>
       <c r="E12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5"/>
       <c r="B13" s="6" t="s">
-        <v>1953</v>
+        <v>1954</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>1954</v>
+        <v>1955</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>1955</v>
+        <v>1956</v>
       </c>
       <c r="E13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5"/>
       <c r="B14" s="6" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>1958</v>
+        <v>1959</v>
       </c>
       <c r="E14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5"/>
       <c r="B15" s="11" t="s">
-        <v>1959</v>
+        <v>1960</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>1960</v>
+        <v>1961</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>1961</v>
+        <v>1962</v>
       </c>
       <c r="E15" s="3"/>
     </row>
@@ -10470,78 +10473,78 @@
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
-        <v>1962</v>
+        <v>1963</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>1963</v>
+        <v>1964</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>1964</v>
+        <v>1965</v>
       </c>
       <c r="E2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5"/>
       <c r="B3" s="6" t="s">
-        <v>1965</v>
+        <v>1966</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>1966</v>
+        <v>1967</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>1967</v>
+        <v>1968</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5"/>
       <c r="B4" s="6" t="s">
-        <v>1968</v>
+        <v>1969</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>1969</v>
+        <v>1970</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>1970</v>
+        <v>1971</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5"/>
       <c r="B5" s="6" t="s">
-        <v>1971</v>
+        <v>1972</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>1972</v>
+        <v>1973</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>1973</v>
+        <v>1974</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
       <c r="B6" s="6" t="s">
-        <v>1974</v>
+        <v>1975</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1975</v>
+        <v>1976</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>1976</v>
+        <v>1977</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
       <c r="B7" s="6" t="s">
-        <v>1977</v>
+        <v>1978</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>1978</v>
+        <v>1979</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>1979</v>
+        <v>1980</v>
       </c>
       <c r="E7" s="3"/>
     </row>
@@ -10551,166 +10554,166 @@
         <v>55</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>1980</v>
+        <v>1981</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>1981</v>
+        <v>1982</v>
       </c>
       <c r="E8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5"/>
       <c r="B9" s="6" t="s">
-        <v>1982</v>
+        <v>1983</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>1983</v>
+        <v>1984</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>1984</v>
+        <v>1985</v>
       </c>
       <c r="E9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5"/>
       <c r="B10" s="6" t="s">
-        <v>1985</v>
+        <v>1986</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>1986</v>
+        <v>1987</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>1987</v>
+        <v>1988</v>
       </c>
       <c r="E10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
       <c r="B11" s="6" t="s">
-        <v>1988</v>
+        <v>1989</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>1989</v>
+        <v>1990</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>1990</v>
+        <v>1991</v>
       </c>
       <c r="E11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5"/>
       <c r="B12" s="6" t="s">
-        <v>1991</v>
+        <v>1992</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>1992</v>
+        <v>1993</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>1993</v>
+        <v>1994</v>
       </c>
       <c r="E12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5"/>
       <c r="B13" s="6" t="s">
-        <v>1994</v>
+        <v>1995</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>1995</v>
+        <v>1996</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>1996</v>
+        <v>1997</v>
       </c>
       <c r="E13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5"/>
       <c r="B14" s="6" t="s">
-        <v>1997</v>
+        <v>1998</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>1998</v>
+        <v>1999</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>1999</v>
+        <v>2000</v>
       </c>
       <c r="E14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5"/>
       <c r="B15" s="6" t="s">
-        <v>2000</v>
+        <v>2001</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>2001</v>
+        <v>2002</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>2002</v>
+        <v>2003</v>
       </c>
       <c r="E15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5"/>
       <c r="B16" s="6" t="s">
-        <v>2003</v>
+        <v>2004</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>2004</v>
+        <v>2005</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>2005</v>
+        <v>2006</v>
       </c>
       <c r="E16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5"/>
       <c r="B17" s="6" t="s">
-        <v>2006</v>
+        <v>2007</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>2007</v>
+        <v>2008</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>2008</v>
+        <v>2009</v>
       </c>
       <c r="E17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5"/>
       <c r="B18" s="6" t="s">
-        <v>2009</v>
+        <v>2010</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>2010</v>
+        <v>2011</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>2011</v>
+        <v>2012</v>
       </c>
       <c r="E18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5"/>
       <c r="B19" s="6" t="s">
-        <v>2012</v>
+        <v>2013</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>2013</v>
+        <v>2014</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>2014</v>
+        <v>2015</v>
       </c>
       <c r="E19" s="3"/>
     </row>
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5"/>
       <c r="B20" s="11" t="s">
-        <v>2015</v>
+        <v>2016</v>
       </c>
       <c r="C20" s="12" t="s">
-        <v>2016</v>
+        <v>2017</v>
       </c>
       <c r="D20" s="21" t="s">
-        <v>2017</v>
+        <v>2018</v>
       </c>
       <c r="E20" s="3"/>
     </row>
@@ -10760,52 +10763,52 @@
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
-        <v>2018</v>
+        <v>2019</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>2019</v>
+        <v>2020</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>2020</v>
+        <v>2021</v>
       </c>
       <c r="E2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5"/>
       <c r="B3" s="6" t="s">
-        <v>2021</v>
+        <v>2022</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>2022</v>
+        <v>2023</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>2023</v>
+        <v>2024</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5"/>
       <c r="B4" s="6" t="s">
-        <v>2024</v>
+        <v>2025</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>2025</v>
+        <v>2026</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>2026</v>
+        <v>2027</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5"/>
       <c r="B5" s="6" t="s">
-        <v>2027</v>
+        <v>2028</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>2028</v>
+        <v>2029</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>2029</v>
+        <v>2030</v>
       </c>
       <c r="E5" s="3"/>
     </row>
@@ -10890,78 +10893,78 @@
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
-        <v>2030</v>
+        <v>2031</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>2031</v>
+        <v>2032</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>2032</v>
+        <v>2033</v>
       </c>
       <c r="E2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5"/>
       <c r="B3" s="6" t="s">
-        <v>2033</v>
+        <v>2034</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>2034</v>
+        <v>2035</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>2035</v>
+        <v>2036</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5"/>
       <c r="B4" s="6" t="s">
-        <v>2036</v>
+        <v>2037</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>2037</v>
+        <v>2038</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>2038</v>
+        <v>2039</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5"/>
       <c r="B5" s="6" t="s">
-        <v>2039</v>
+        <v>2040</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>2040</v>
+        <v>2041</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>2041</v>
+        <v>2042</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
       <c r="B6" s="6" t="s">
-        <v>2042</v>
+        <v>2043</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>2043</v>
+        <v>2044</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>2044</v>
+        <v>2045</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
       <c r="B7" s="6" t="s">
-        <v>2045</v>
+        <v>2046</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>2046</v>
+        <v>2047</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>2047</v>
+        <v>2048</v>
       </c>
       <c r="E7" s="3"/>
     </row>
@@ -11032,26 +11035,26 @@
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
-        <v>2048</v>
+        <v>2049</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>2049</v>
+        <v>2050</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>2050</v>
+        <v>2051</v>
       </c>
       <c r="E2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5"/>
       <c r="B3" s="6" t="s">
-        <v>2051</v>
+        <v>2052</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>2052</v>
+        <v>2053</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>2053</v>
+        <v>2054</v>
       </c>
       <c r="E3" s="3"/>
     </row>
@@ -11061,205 +11064,205 @@
         <v>166</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>2054</v>
+        <v>2055</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>2055</v>
+        <v>2056</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5"/>
       <c r="B5" s="6" t="s">
-        <v>2056</v>
+        <v>2057</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>2057</v>
+        <v>2058</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>2058</v>
+        <v>2059</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
       <c r="B6" s="6" t="s">
-        <v>2059</v>
+        <v>2060</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>2060</v>
+        <v>2061</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>2061</v>
+        <v>2062</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
       <c r="B7" s="6" t="s">
-        <v>2062</v>
+        <v>2063</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>2063</v>
+        <v>2064</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>2064</v>
+        <v>2065</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5"/>
       <c r="B8" s="6" t="s">
-        <v>2065</v>
+        <v>2066</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>2066</v>
+        <v>2067</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>2067</v>
+        <v>2068</v>
       </c>
       <c r="E8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5"/>
       <c r="B9" s="6" t="s">
-        <v>2068</v>
+        <v>2069</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>2069</v>
+        <v>2070</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>2070</v>
+        <v>2071</v>
       </c>
       <c r="E9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5"/>
       <c r="B10" s="6" t="s">
-        <v>2071</v>
+        <v>2072</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>2072</v>
+        <v>2073</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>2073</v>
+        <v>2074</v>
       </c>
       <c r="E10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
       <c r="B11" s="6" t="s">
-        <v>2074</v>
+        <v>2075</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>2075</v>
+        <v>2076</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>2076</v>
+        <v>2077</v>
       </c>
       <c r="E11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5"/>
       <c r="B12" s="6" t="s">
-        <v>2077</v>
+        <v>2078</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>2078</v>
+        <v>2079</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>2079</v>
+        <v>2080</v>
       </c>
       <c r="E12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5"/>
       <c r="B13" s="6" t="s">
-        <v>2080</v>
+        <v>2081</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>2081</v>
+        <v>2082</v>
       </c>
       <c r="D13" s="21" t="s">
-        <v>2082</v>
+        <v>2083</v>
       </c>
       <c r="E13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5"/>
       <c r="B14" s="6" t="s">
-        <v>2083</v>
+        <v>2084</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>2084</v>
+        <v>2085</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>2085</v>
+        <v>2086</v>
       </c>
       <c r="E14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5"/>
       <c r="B15" s="6" t="s">
-        <v>2086</v>
+        <v>2087</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>2087</v>
+        <v>2088</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>2088</v>
+        <v>2089</v>
       </c>
       <c r="E15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5"/>
       <c r="B16" s="6" t="s">
-        <v>2089</v>
+        <v>2090</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>2090</v>
+        <v>2091</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>2091</v>
+        <v>2092</v>
       </c>
       <c r="E16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5"/>
       <c r="B17" s="6" t="s">
-        <v>2092</v>
+        <v>2093</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>2093</v>
+        <v>2094</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>2094</v>
+        <v>2095</v>
       </c>
       <c r="E17" s="3"/>
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5"/>
       <c r="B18" s="6" t="s">
-        <v>2095</v>
+        <v>2096</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>2096</v>
+        <v>2097</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>2097</v>
+        <v>2098</v>
       </c>
       <c r="E18" s="3"/>
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5"/>
       <c r="B19" s="11" t="s">
-        <v>2098</v>
+        <v>2099</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>2099</v>
+        <v>2100</v>
       </c>
       <c r="D19" s="21" t="s">
-        <v>2100</v>
+        <v>2101</v>
       </c>
       <c r="E19" s="3"/>
     </row>
@@ -11309,10 +11312,10 @@
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
-        <v>2101</v>
+        <v>2102</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>2102</v>
+        <v>2103</v>
       </c>
       <c r="D2" s="19"/>
       <c r="E2" s="3"/>
@@ -11320,10 +11323,10 @@
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5"/>
       <c r="B3" s="6" t="s">
-        <v>2103</v>
+        <v>2104</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>2104</v>
+        <v>2105</v>
       </c>
       <c r="D3" s="19"/>
       <c r="E3" s="3"/>
@@ -11331,10 +11334,10 @@
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5"/>
       <c r="B4" s="6" t="s">
-        <v>2105</v>
+        <v>2106</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>2106</v>
+        <v>2107</v>
       </c>
       <c r="D4" s="19"/>
       <c r="E4" s="3"/>
@@ -11342,10 +11345,10 @@
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5"/>
       <c r="B5" s="6" t="s">
-        <v>2107</v>
+        <v>2108</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>2108</v>
+        <v>2109</v>
       </c>
       <c r="D5" s="19"/>
       <c r="E5" s="3"/>
@@ -11353,10 +11356,10 @@
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
       <c r="B6" s="6" t="s">
-        <v>2109</v>
+        <v>2110</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>2110</v>
+        <v>2111</v>
       </c>
       <c r="D6" s="19"/>
       <c r="E6" s="3"/>
@@ -11364,10 +11367,10 @@
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
       <c r="B7" s="6" t="s">
-        <v>2111</v>
+        <v>2112</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>2112</v>
+        <v>2113</v>
       </c>
       <c r="D7" s="19"/>
       <c r="E7" s="3"/>
@@ -11375,10 +11378,10 @@
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5"/>
       <c r="B8" s="6" t="s">
-        <v>2113</v>
+        <v>2114</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>2114</v>
+        <v>2115</v>
       </c>
       <c r="D8" s="19"/>
       <c r="E8" s="3"/>
@@ -11386,10 +11389,10 @@
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5"/>
       <c r="B9" s="6" t="s">
-        <v>2115</v>
+        <v>2116</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>2116</v>
+        <v>2117</v>
       </c>
       <c r="D9" s="19"/>
       <c r="E9" s="3"/>
@@ -11397,10 +11400,10 @@
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5"/>
       <c r="B10" s="6" t="s">
-        <v>2117</v>
+        <v>2118</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>2118</v>
+        <v>2119</v>
       </c>
       <c r="D10" s="19"/>
       <c r="E10" s="3"/>
@@ -11408,10 +11411,10 @@
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
       <c r="B11" s="6" t="s">
-        <v>2119</v>
+        <v>2120</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>2120</v>
+        <v>2121</v>
       </c>
       <c r="D11" s="19"/>
       <c r="E11" s="3"/>
@@ -11419,10 +11422,10 @@
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5"/>
       <c r="B12" s="11" t="s">
-        <v>2121</v>
+        <v>2122</v>
       </c>
       <c r="C12" s="12" t="s">
-        <v>2122</v>
+        <v>2123</v>
       </c>
       <c r="D12" s="19"/>
       <c r="E12" s="3"/>
@@ -13644,104 +13647,104 @@
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
-        <v>2123</v>
+        <v>2124</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>2124</v>
+        <v>2125</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>2125</v>
+        <v>2126</v>
       </c>
       <c r="E2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5"/>
       <c r="B3" s="6" t="s">
-        <v>2126</v>
+        <v>2127</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>2127</v>
+        <v>2128</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>2128</v>
+        <v>2129</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5"/>
       <c r="B4" s="6" t="s">
-        <v>2129</v>
+        <v>2130</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>2130</v>
+        <v>2131</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>2131</v>
+        <v>2132</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5"/>
       <c r="B5" s="6" t="s">
-        <v>2132</v>
+        <v>2133</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>2133</v>
+        <v>2134</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>2134</v>
+        <v>2135</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
       <c r="B6" s="6" t="s">
-        <v>2135</v>
+        <v>2136</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>2136</v>
+        <v>2137</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>2137</v>
+        <v>2138</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
       <c r="B7" s="6" t="s">
-        <v>2138</v>
+        <v>2139</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>2139</v>
+        <v>2140</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>2140</v>
+        <v>2141</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5"/>
       <c r="B8" s="6" t="s">
-        <v>2141</v>
+        <v>2142</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>2142</v>
+        <v>2143</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>2143</v>
+        <v>2144</v>
       </c>
       <c r="E8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5"/>
       <c r="B9" s="6" t="s">
-        <v>2144</v>
+        <v>2145</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>2145</v>
+        <v>2146</v>
       </c>
       <c r="D9" s="21" t="s">
-        <v>2146</v>
+        <v>2147</v>
       </c>
       <c r="E9" s="3"/>
     </row>
@@ -13798,10 +13801,10 @@
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
-        <v>2147</v>
+        <v>2148</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>2148</v>
+        <v>2149</v>
       </c>
       <c r="D2" s="19"/>
       <c r="E2" s="3"/>
@@ -13809,10 +13812,10 @@
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5"/>
       <c r="B3" s="6" t="s">
-        <v>2149</v>
+        <v>2150</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>2150</v>
+        <v>2151</v>
       </c>
       <c r="D3" s="19"/>
       <c r="E3" s="3"/>
@@ -13820,10 +13823,10 @@
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5"/>
       <c r="B4" s="6" t="s">
-        <v>2151</v>
+        <v>2152</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>2152</v>
+        <v>2153</v>
       </c>
       <c r="D4" s="19"/>
       <c r="E4" s="3"/>
@@ -13831,10 +13834,10 @@
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5"/>
       <c r="B5" s="6" t="s">
-        <v>2153</v>
+        <v>2154</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>2154</v>
+        <v>2155</v>
       </c>
       <c r="D5" s="19"/>
       <c r="E5" s="3"/>
@@ -13842,10 +13845,10 @@
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
       <c r="B6" s="6" t="s">
-        <v>2155</v>
+        <v>2156</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>2156</v>
+        <v>2157</v>
       </c>
       <c r="D6" s="19"/>
       <c r="E6" s="3"/>
@@ -13853,10 +13856,10 @@
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
       <c r="B7" s="6" t="s">
-        <v>2157</v>
+        <v>2158</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>2158</v>
+        <v>2159</v>
       </c>
       <c r="D7" s="19"/>
       <c r="E7" s="3"/>
@@ -13864,10 +13867,10 @@
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5"/>
       <c r="B8" s="6" t="s">
-        <v>2159</v>
+        <v>2160</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>2160</v>
+        <v>2161</v>
       </c>
       <c r="D8" s="19"/>
       <c r="E8" s="3"/>
@@ -13875,10 +13878,10 @@
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5"/>
       <c r="B9" s="6" t="s">
-        <v>2161</v>
+        <v>2162</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>2162</v>
+        <v>2163</v>
       </c>
       <c r="D9" s="19"/>
       <c r="E9" s="3"/>
@@ -13886,10 +13889,10 @@
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5"/>
       <c r="B10" s="6" t="s">
-        <v>2163</v>
+        <v>2164</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>2164</v>
+        <v>2165</v>
       </c>
       <c r="D10" s="19"/>
       <c r="E10" s="3"/>
@@ -13897,10 +13900,10 @@
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
       <c r="B11" s="6" t="s">
-        <v>2165</v>
+        <v>2166</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>2166</v>
+        <v>2167</v>
       </c>
       <c r="D11" s="19"/>
       <c r="E11" s="3"/>
@@ -13908,10 +13911,10 @@
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5"/>
       <c r="B12" s="6" t="s">
-        <v>2167</v>
+        <v>2168</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>2168</v>
+        <v>2169</v>
       </c>
       <c r="D12" s="19"/>
       <c r="E12" s="3"/>
@@ -13919,10 +13922,10 @@
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5"/>
       <c r="B13" s="6" t="s">
-        <v>2169</v>
+        <v>2170</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>2170</v>
+        <v>2171</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="3"/>
@@ -13930,10 +13933,10 @@
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5"/>
       <c r="B14" s="6" t="s">
-        <v>2171</v>
+        <v>2172</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>2172</v>
+        <v>2173</v>
       </c>
       <c r="D14" s="19"/>
       <c r="E14" s="3"/>
@@ -13941,10 +13944,10 @@
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5"/>
       <c r="B15" s="6" t="s">
-        <v>2173</v>
+        <v>2174</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>2174</v>
+        <v>2175</v>
       </c>
       <c r="D15" s="19"/>
       <c r="E15" s="3"/>
@@ -13952,10 +13955,10 @@
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5"/>
       <c r="B16" s="6" t="s">
-        <v>2175</v>
+        <v>2176</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>2176</v>
+        <v>2177</v>
       </c>
       <c r="D16" s="19"/>
       <c r="E16" s="3"/>
@@ -13963,10 +13966,10 @@
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5"/>
       <c r="B17" s="6" t="s">
-        <v>2177</v>
+        <v>2178</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>2178</v>
+        <v>2179</v>
       </c>
       <c r="D17" s="19"/>
       <c r="E17" s="3"/>
@@ -13974,10 +13977,10 @@
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5"/>
       <c r="B18" s="6" t="s">
-        <v>2179</v>
+        <v>2180</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>2180</v>
+        <v>2181</v>
       </c>
       <c r="D18" s="19"/>
       <c r="E18" s="3"/>
@@ -13985,10 +13988,10 @@
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5"/>
       <c r="B19" s="6" t="s">
-        <v>2181</v>
+        <v>2182</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>2182</v>
+        <v>2183</v>
       </c>
       <c r="D19" s="19"/>
       <c r="E19" s="3"/>
@@ -13996,10 +13999,10 @@
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5"/>
       <c r="B20" s="6" t="s">
-        <v>2183</v>
+        <v>2184</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>2184</v>
+        <v>2185</v>
       </c>
       <c r="D20" s="19"/>
       <c r="E20" s="3"/>
@@ -14007,10 +14010,10 @@
     <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="5"/>
       <c r="B21" s="6" t="s">
-        <v>2185</v>
+        <v>2186</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>2186</v>
+        <v>2187</v>
       </c>
       <c r="D21" s="19"/>
       <c r="E21" s="3"/>
@@ -14018,10 +14021,10 @@
     <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5"/>
       <c r="B22" s="6" t="s">
-        <v>2187</v>
+        <v>2188</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>2188</v>
+        <v>2189</v>
       </c>
       <c r="D22" s="19"/>
       <c r="E22" s="3"/>
@@ -14029,10 +14032,10 @@
     <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5"/>
       <c r="B23" s="6" t="s">
-        <v>2189</v>
+        <v>2190</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>2190</v>
+        <v>2191</v>
       </c>
       <c r="D23" s="19"/>
       <c r="E23" s="3"/>
@@ -14040,10 +14043,10 @@
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5"/>
       <c r="B24" s="6" t="s">
-        <v>2191</v>
+        <v>2192</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>2192</v>
+        <v>2193</v>
       </c>
       <c r="D24" s="19"/>
       <c r="E24" s="3"/>
@@ -14051,10 +14054,10 @@
     <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="5"/>
       <c r="B25" s="6" t="s">
-        <v>2193</v>
+        <v>2194</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>2194</v>
+        <v>2195</v>
       </c>
       <c r="D25" s="19"/>
       <c r="E25" s="3"/>
@@ -14062,10 +14065,10 @@
     <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5"/>
       <c r="B26" s="6" t="s">
-        <v>2195</v>
+        <v>2196</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>2196</v>
+        <v>2197</v>
       </c>
       <c r="D26" s="19"/>
       <c r="E26" s="3"/>
@@ -14073,10 +14076,10 @@
     <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="5"/>
       <c r="B27" s="6" t="s">
-        <v>2197</v>
+        <v>2198</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>2198</v>
+        <v>2199</v>
       </c>
       <c r="D27" s="19"/>
       <c r="E27" s="3"/>
@@ -14084,10 +14087,10 @@
     <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="5"/>
       <c r="B28" s="6" t="s">
-        <v>2199</v>
+        <v>2200</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>2200</v>
+        <v>2201</v>
       </c>
       <c r="D28" s="19"/>
       <c r="E28" s="3"/>
@@ -14095,10 +14098,10 @@
     <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="5"/>
       <c r="B29" s="6" t="s">
-        <v>2201</v>
+        <v>2202</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>2202</v>
+        <v>2203</v>
       </c>
       <c r="D29" s="19"/>
       <c r="E29" s="3"/>
@@ -14106,10 +14109,10 @@
     <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="5"/>
       <c r="B30" s="6" t="s">
-        <v>2203</v>
+        <v>2204</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>2204</v>
+        <v>2205</v>
       </c>
       <c r="D30" s="19"/>
       <c r="E30" s="3"/>
@@ -14117,10 +14120,10 @@
     <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="5"/>
       <c r="B31" s="6" t="s">
-        <v>2205</v>
+        <v>2206</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>2206</v>
+        <v>2207</v>
       </c>
       <c r="D31" s="19"/>
       <c r="E31" s="3"/>
@@ -14128,10 +14131,10 @@
     <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="5"/>
       <c r="B32" s="11" t="s">
-        <v>2207</v>
+        <v>2208</v>
       </c>
       <c r="C32" s="12" t="s">
-        <v>2208</v>
+        <v>2209</v>
       </c>
       <c r="D32" s="19"/>
       <c r="E32" s="3"/>
@@ -14182,10 +14185,10 @@
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
-        <v>2209</v>
+        <v>2210</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>2210</v>
+        <v>2211</v>
       </c>
       <c r="D2" s="19"/>
       <c r="E2" s="3"/>
@@ -14193,10 +14196,10 @@
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5"/>
       <c r="B3" s="6" t="s">
-        <v>2211</v>
+        <v>2212</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>2212</v>
+        <v>2213</v>
       </c>
       <c r="D3" s="19"/>
       <c r="E3" s="3"/>
@@ -14204,10 +14207,10 @@
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5"/>
       <c r="B4" s="6" t="s">
-        <v>2213</v>
+        <v>2214</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>2214</v>
+        <v>2215</v>
       </c>
       <c r="D4" s="19"/>
       <c r="E4" s="3"/>
@@ -14215,10 +14218,10 @@
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5"/>
       <c r="B5" s="6" t="s">
-        <v>2215</v>
+        <v>2216</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>2216</v>
+        <v>2217</v>
       </c>
       <c r="D5" s="19"/>
       <c r="E5" s="3"/>
@@ -14304,52 +14307,52 @@
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
-        <v>2217</v>
+        <v>2218</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>2218</v>
+        <v>2219</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>2219</v>
+        <v>2220</v>
       </c>
       <c r="E2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5"/>
       <c r="B3" s="6" t="s">
-        <v>2220</v>
+        <v>2221</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>2221</v>
+        <v>2222</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>2222</v>
+        <v>2223</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5"/>
       <c r="B4" s="6" t="s">
-        <v>2223</v>
+        <v>2224</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>2224</v>
+        <v>2225</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>2225</v>
+        <v>2226</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5"/>
       <c r="B5" s="6" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>2226</v>
+        <v>2227</v>
       </c>
       <c r="E5" s="3"/>
     </row>
@@ -14434,67 +14437,67 @@
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
-        <v>2227</v>
+        <v>2228</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>2228</v>
+        <v>2229</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>2229</v>
+        <v>2230</v>
       </c>
       <c r="E2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5"/>
       <c r="B3" s="6" t="s">
-        <v>2230</v>
+        <v>2231</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>2231</v>
+        <v>2232</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>2232</v>
+        <v>2233</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5"/>
       <c r="B4" s="6" t="s">
-        <v>2233</v>
+        <v>2234</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>2234</v>
+        <v>2235</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>2235</v>
+        <v>2236</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="14" t="s">
-        <v>2236</v>
+        <v>2237</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>2237</v>
+        <v>2238</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>2238</v>
+        <v>2239</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>2239</v>
+        <v>2240</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
       <c r="B6" s="6" t="s">
-        <v>2240</v>
+        <v>2241</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>2241</v>
+        <v>2242</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>2242</v>
+        <v>2243</v>
       </c>
       <c r="E6" s="3"/>
     </row>
@@ -14571,81 +14574,81 @@
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="14" t="s">
-        <v>2243</v>
+        <v>2244</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>2244</v>
+        <v>2245</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>2245</v>
+        <v>2246</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>2246</v>
+        <v>2247</v>
       </c>
       <c r="E2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5"/>
       <c r="B3" s="6" t="s">
-        <v>2247</v>
+        <v>2248</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>2248</v>
+        <v>2249</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>2249</v>
+        <v>2250</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5"/>
       <c r="B4" s="6" t="s">
-        <v>2250</v>
+        <v>2251</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>2251</v>
+        <v>2252</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>2252</v>
+        <v>2253</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5"/>
       <c r="B5" s="6" t="s">
-        <v>2253</v>
+        <v>2254</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>2254</v>
+        <v>2255</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>2255</v>
+        <v>2256</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
       <c r="B6" s="6" t="s">
-        <v>2256</v>
+        <v>2257</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>2257</v>
+        <v>2258</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>2258</v>
+        <v>2259</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
       <c r="B7" s="6" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>2259</v>
+        <v>2260</v>
       </c>
       <c r="E7" s="3"/>
     </row>
@@ -14716,36 +14719,36 @@
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
-        <v>2260</v>
+        <v>2261</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>2260</v>
+        <v>2261</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>2261</v>
+        <v>2262</v>
       </c>
       <c r="E2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5"/>
       <c r="B3" s="6" t="s">
-        <v>2262</v>
+        <v>2263</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>2262</v>
+        <v>2263</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>2263</v>
+        <v>2264</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5"/>
       <c r="B4" s="6" t="s">
-        <v>2264</v>
+        <v>2265</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>2265</v>
+        <v>2266</v>
       </c>
       <c r="D4" s="19"/>
       <c r="E4" s="3"/>
@@ -14753,10 +14756,10 @@
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5"/>
       <c r="B5" s="6" t="s">
-        <v>2266</v>
+        <v>2267</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>2267</v>
+        <v>2268</v>
       </c>
       <c r="D5" s="19"/>
       <c r="E5" s="3"/>
@@ -14764,10 +14767,10 @@
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
       <c r="B6" s="6" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1957</v>
+        <v>1958</v>
       </c>
       <c r="D6" s="19"/>
       <c r="E6" s="3"/>
@@ -14846,10 +14849,10 @@
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
-        <v>2268</v>
+        <v>2269</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>2269</v>
+        <v>2270</v>
       </c>
       <c r="D2" s="19"/>
       <c r="E2" s="3"/>
@@ -14857,10 +14860,10 @@
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5"/>
       <c r="B3" s="6" t="s">
-        <v>2270</v>
+        <v>2271</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>2271</v>
+        <v>2272</v>
       </c>
       <c r="D3" s="19"/>
       <c r="E3" s="3"/>
@@ -14868,10 +14871,10 @@
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5"/>
       <c r="B4" s="6" t="s">
-        <v>2272</v>
+        <v>2273</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>2273</v>
+        <v>2274</v>
       </c>
       <c r="D4" s="19"/>
       <c r="E4" s="3"/>
@@ -14879,10 +14882,10 @@
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5"/>
       <c r="B5" s="6" t="s">
-        <v>2274</v>
+        <v>2275</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>2275</v>
+        <v>2276</v>
       </c>
       <c r="D5" s="19"/>
       <c r="E5" s="3"/>
@@ -14890,10 +14893,10 @@
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
       <c r="B6" s="6" t="s">
-        <v>2276</v>
+        <v>2277</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>2277</v>
+        <v>2278</v>
       </c>
       <c r="D6" s="19"/>
       <c r="E6" s="3"/>
@@ -14901,10 +14904,10 @@
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
       <c r="B7" s="6" t="s">
-        <v>2278</v>
+        <v>2279</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>2279</v>
+        <v>2280</v>
       </c>
       <c r="D7" s="19"/>
       <c r="E7" s="3"/>
@@ -14912,10 +14915,10 @@
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5"/>
       <c r="B8" s="6" t="s">
-        <v>1956</v>
+        <v>1957</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>2280</v>
+        <v>2281</v>
       </c>
       <c r="D8" s="19"/>
       <c r="E8" s="3"/>
@@ -14979,65 +14982,65 @@
     </row>
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="2" t="s">
-        <v>2281</v>
+        <v>2282</v>
       </c>
       <c r="B2" s="22" t="s">
-        <v>2282</v>
+        <v>2283</v>
       </c>
       <c r="C2" s="23" t="s">
-        <v>2283</v>
+        <v>2284</v>
       </c>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="2" t="s">
-        <v>2284</v>
+        <v>2285</v>
       </c>
       <c r="B3" s="22" t="s">
-        <v>2285</v>
+        <v>2286</v>
       </c>
       <c r="C3" s="23" t="s">
-        <v>2286</v>
+        <v>2287</v>
       </c>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="2" t="s">
-        <v>2287</v>
+        <v>2288</v>
       </c>
       <c r="B4" s="22" t="s">
-        <v>2282</v>
+        <v>2283</v>
       </c>
       <c r="C4" s="23" t="s">
-        <v>2283</v>
+        <v>2284</v>
       </c>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="2" t="s">
-        <v>2288</v>
+        <v>2289</v>
       </c>
       <c r="B5" s="22" t="s">
-        <v>2282</v>
+        <v>2283</v>
       </c>
       <c r="C5" s="23" t="s">
-        <v>2283</v>
+        <v>2284</v>
       </c>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="2" t="s">
-        <v>2289</v>
+        <v>2290</v>
       </c>
       <c r="B6" s="22" t="s">
-        <v>2285</v>
+        <v>2286</v>
       </c>
       <c r="C6" s="23" t="s">
-        <v>2286</v>
+        <v>2287</v>
       </c>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
@@ -15116,10 +15119,10 @@
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
-        <v>2290</v>
+        <v>2291</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>2291</v>
+        <v>2292</v>
       </c>
       <c r="D2" s="19"/>
       <c r="E2" s="3"/>
@@ -15127,10 +15130,10 @@
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5"/>
       <c r="B3" s="6" t="s">
-        <v>2292</v>
+        <v>2293</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>2293</v>
+        <v>2294</v>
       </c>
       <c r="D3" s="19"/>
       <c r="E3" s="3"/>
@@ -15138,10 +15141,10 @@
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5"/>
       <c r="B4" s="6" t="s">
-        <v>2294</v>
+        <v>2295</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>2295</v>
+        <v>2296</v>
       </c>
       <c r="D4" s="19"/>
       <c r="E4" s="3"/>
@@ -15149,10 +15152,10 @@
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5"/>
       <c r="B5" s="6" t="s">
-        <v>2296</v>
+        <v>2297</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>2297</v>
+        <v>2298</v>
       </c>
       <c r="D5" s="19"/>
       <c r="E5" s="3"/>
@@ -15160,10 +15163,10 @@
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
       <c r="B6" s="6" t="s">
-        <v>2298</v>
+        <v>2299</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>2299</v>
+        <v>2300</v>
       </c>
       <c r="D6" s="19"/>
       <c r="E6" s="3"/>
@@ -15171,10 +15174,10 @@
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
       <c r="B7" s="6" t="s">
-        <v>2300</v>
+        <v>2301</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>2301</v>
+        <v>2302</v>
       </c>
       <c r="D7" s="19"/>
       <c r="E7" s="3"/>
@@ -15182,10 +15185,10 @@
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5"/>
       <c r="B8" s="6" t="s">
-        <v>2302</v>
+        <v>2303</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>2303</v>
+        <v>2304</v>
       </c>
       <c r="D8" s="19"/>
       <c r="E8" s="3"/>
@@ -15193,10 +15196,10 @@
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5"/>
       <c r="B9" s="6" t="s">
-        <v>2304</v>
+        <v>2305</v>
       </c>
       <c r="C9" s="7" t="s">
-        <v>2305</v>
+        <v>2306</v>
       </c>
       <c r="D9" s="19"/>
       <c r="E9" s="3"/>
@@ -15204,10 +15207,10 @@
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5"/>
       <c r="B10" s="6" t="s">
-        <v>2306</v>
+        <v>2307</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>2307</v>
+        <v>2308</v>
       </c>
       <c r="D10" s="19"/>
       <c r="E10" s="3"/>
@@ -15215,2346 +15218,2346 @@
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
       <c r="B11" s="6" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>2309</v>
+        <v>2310</v>
       </c>
       <c r="D11" s="19"/>
       <c r="E11" s="2" t="s">
-        <v>2290</v>
+        <v>2291</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5"/>
       <c r="B12" s="6" t="s">
-        <v>2310</v>
+        <v>2311</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>2311</v>
+        <v>2312</v>
       </c>
       <c r="D12" s="19"/>
       <c r="E12" s="2" t="s">
-        <v>2292</v>
+        <v>2293</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5"/>
       <c r="B13" s="6" t="s">
-        <v>2312</v>
+        <v>2313</v>
       </c>
       <c r="C13" s="7" t="s">
-        <v>2313</v>
+        <v>2314</v>
       </c>
       <c r="D13" s="19"/>
       <c r="E13" s="2" t="s">
-        <v>2292</v>
+        <v>2293</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5"/>
       <c r="B14" s="6" t="s">
-        <v>2314</v>
+        <v>2315</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>2315</v>
+        <v>2316</v>
       </c>
       <c r="D14" s="19"/>
       <c r="E14" s="2" t="s">
-        <v>2294</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5"/>
       <c r="B15" s="6" t="s">
-        <v>2316</v>
+        <v>2317</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>2317</v>
+        <v>2318</v>
       </c>
       <c r="D15" s="19"/>
       <c r="E15" s="2" t="s">
-        <v>2294</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5"/>
       <c r="B16" s="6" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>2319</v>
+        <v>2320</v>
       </c>
       <c r="D16" s="19"/>
       <c r="E16" s="2" t="s">
-        <v>2294</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5"/>
       <c r="B17" s="6" t="s">
-        <v>2320</v>
+        <v>2321</v>
       </c>
       <c r="C17" s="7" t="s">
-        <v>2321</v>
+        <v>2322</v>
       </c>
       <c r="D17" s="19"/>
       <c r="E17" s="2" t="s">
-        <v>2294</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A18" s="5"/>
       <c r="B18" s="6" t="s">
-        <v>2322</v>
+        <v>2323</v>
       </c>
       <c r="C18" s="7" t="s">
-        <v>2323</v>
+        <v>2324</v>
       </c>
       <c r="D18" s="19"/>
       <c r="E18" s="2" t="s">
-        <v>2294</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A19" s="5"/>
       <c r="B19" s="6" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
       <c r="C19" s="7" t="s">
-        <v>2325</v>
+        <v>2326</v>
       </c>
       <c r="D19" s="19"/>
       <c r="E19" s="2" t="s">
-        <v>2294</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A20" s="5"/>
       <c r="B20" s="6" t="s">
-        <v>2326</v>
+        <v>2327</v>
       </c>
       <c r="C20" s="7" t="s">
-        <v>2327</v>
+        <v>2328</v>
       </c>
       <c r="D20" s="19"/>
       <c r="E20" s="2" t="s">
-        <v>2294</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A21" s="5"/>
       <c r="B21" s="6" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
       <c r="C21" s="7" t="s">
-        <v>2329</v>
+        <v>2330</v>
       </c>
       <c r="D21" s="19"/>
       <c r="E21" s="2" t="s">
-        <v>2294</v>
+        <v>2295</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A22" s="5"/>
       <c r="B22" s="6" t="s">
-        <v>2330</v>
+        <v>2331</v>
       </c>
       <c r="C22" s="7" t="s">
-        <v>2331</v>
+        <v>2332</v>
       </c>
       <c r="D22" s="19"/>
       <c r="E22" s="2" t="s">
-        <v>2296</v>
+        <v>2297</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A23" s="5"/>
       <c r="B23" s="6" t="s">
-        <v>2332</v>
+        <v>2333</v>
       </c>
       <c r="C23" s="7" t="s">
-        <v>2333</v>
+        <v>2334</v>
       </c>
       <c r="D23" s="19"/>
       <c r="E23" s="2" t="s">
-        <v>2296</v>
+        <v>2297</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A24" s="5"/>
       <c r="B24" s="6" t="s">
-        <v>2334</v>
+        <v>2335</v>
       </c>
       <c r="C24" s="7" t="s">
-        <v>2335</v>
+        <v>2336</v>
       </c>
       <c r="D24" s="19"/>
       <c r="E24" s="2" t="s">
-        <v>2296</v>
+        <v>2297</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A25" s="5"/>
       <c r="B25" s="6" t="s">
-        <v>2336</v>
+        <v>2337</v>
       </c>
       <c r="C25" s="7" t="s">
-        <v>2337</v>
+        <v>2338</v>
       </c>
       <c r="D25" s="19"/>
       <c r="E25" s="2" t="s">
-        <v>2298</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A26" s="5"/>
       <c r="B26" s="6" t="s">
-        <v>2338</v>
+        <v>2339</v>
       </c>
       <c r="C26" s="7" t="s">
-        <v>2339</v>
+        <v>2340</v>
       </c>
       <c r="D26" s="19"/>
       <c r="E26" s="2" t="s">
-        <v>2298</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A27" s="5"/>
       <c r="B27" s="6" t="s">
-        <v>2340</v>
+        <v>2341</v>
       </c>
       <c r="C27" s="7" t="s">
-        <v>2341</v>
+        <v>2342</v>
       </c>
       <c r="D27" s="19"/>
       <c r="E27" s="2" t="s">
-        <v>2298</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A28" s="5"/>
       <c r="B28" s="6" t="s">
-        <v>2342</v>
+        <v>2343</v>
       </c>
       <c r="C28" s="7" t="s">
-        <v>2343</v>
+        <v>2344</v>
       </c>
       <c r="D28" s="19"/>
       <c r="E28" s="2" t="s">
-        <v>2298</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A29" s="5"/>
       <c r="B29" s="6" t="s">
-        <v>2344</v>
+        <v>2345</v>
       </c>
       <c r="C29" s="7" t="s">
-        <v>2345</v>
+        <v>2346</v>
       </c>
       <c r="D29" s="19"/>
       <c r="E29" s="2" t="s">
-        <v>2298</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A30" s="5"/>
       <c r="B30" s="6" t="s">
-        <v>2346</v>
+        <v>2347</v>
       </c>
       <c r="C30" s="7" t="s">
-        <v>2347</v>
+        <v>2348</v>
       </c>
       <c r="D30" s="19"/>
       <c r="E30" s="2" t="s">
-        <v>2298</v>
+        <v>2299</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="5"/>
       <c r="B31" s="6" t="s">
-        <v>2348</v>
+        <v>2349</v>
       </c>
       <c r="C31" s="7" t="s">
-        <v>2349</v>
+        <v>2350</v>
       </c>
       <c r="D31" s="19"/>
       <c r="E31" s="2" t="s">
-        <v>2300</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="5"/>
       <c r="B32" s="6" t="s">
-        <v>2350</v>
+        <v>2351</v>
       </c>
       <c r="C32" s="7" t="s">
-        <v>2351</v>
+        <v>2352</v>
       </c>
       <c r="D32" s="19"/>
       <c r="E32" s="2" t="s">
-        <v>2300</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="5"/>
       <c r="B33" s="6" t="s">
-        <v>2352</v>
+        <v>2353</v>
       </c>
       <c r="C33" s="7" t="s">
-        <v>2353</v>
+        <v>2354</v>
       </c>
       <c r="D33" s="19"/>
       <c r="E33" s="2" t="s">
-        <v>2300</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="5"/>
       <c r="B34" s="6" t="s">
-        <v>2354</v>
+        <v>2355</v>
       </c>
       <c r="C34" s="7" t="s">
-        <v>2355</v>
+        <v>2356</v>
       </c>
       <c r="D34" s="19"/>
       <c r="E34" s="2" t="s">
-        <v>2300</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A35" s="5"/>
       <c r="B35" s="6" t="s">
-        <v>2356</v>
+        <v>2357</v>
       </c>
       <c r="C35" s="7" t="s">
-        <v>2357</v>
+        <v>2358</v>
       </c>
       <c r="D35" s="19"/>
       <c r="E35" s="2" t="s">
-        <v>2300</v>
+        <v>2301</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A36" s="5"/>
       <c r="B36" s="6" t="s">
-        <v>2358</v>
+        <v>2359</v>
       </c>
       <c r="C36" s="7" t="s">
-        <v>2359</v>
+        <v>2360</v>
       </c>
       <c r="D36" s="19"/>
       <c r="E36" s="2" t="s">
-        <v>2302</v>
+        <v>2303</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="5"/>
       <c r="B37" s="6" t="s">
-        <v>2360</v>
+        <v>2361</v>
       </c>
       <c r="C37" s="7" t="s">
-        <v>2361</v>
+        <v>2362</v>
       </c>
       <c r="D37" s="19"/>
       <c r="E37" s="2" t="s">
-        <v>2304</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="5"/>
       <c r="B38" s="6" t="s">
-        <v>2362</v>
+        <v>2363</v>
       </c>
       <c r="C38" s="7" t="s">
-        <v>2363</v>
+        <v>2364</v>
       </c>
       <c r="D38" s="19"/>
       <c r="E38" s="2" t="s">
-        <v>2304</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="5"/>
       <c r="B39" s="6" t="s">
-        <v>2364</v>
+        <v>2365</v>
       </c>
       <c r="C39" s="7" t="s">
-        <v>2365</v>
+        <v>2366</v>
       </c>
       <c r="D39" s="19"/>
       <c r="E39" s="2" t="s">
-        <v>2304</v>
+        <v>2305</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="5"/>
       <c r="B40" s="6" t="s">
-        <v>2366</v>
+        <v>2367</v>
       </c>
       <c r="C40" s="7" t="s">
-        <v>2367</v>
+        <v>2368</v>
       </c>
       <c r="D40" s="19"/>
       <c r="E40" s="2" t="s">
-        <v>2306</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="5"/>
       <c r="B41" s="6" t="s">
-        <v>2368</v>
+        <v>2369</v>
       </c>
       <c r="C41" s="7" t="s">
-        <v>2369</v>
+        <v>2370</v>
       </c>
       <c r="D41" s="19"/>
       <c r="E41" s="2" t="s">
-        <v>2306</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="5"/>
       <c r="B42" s="6" t="s">
-        <v>2370</v>
+        <v>2371</v>
       </c>
       <c r="C42" s="7" t="s">
-        <v>2371</v>
+        <v>2372</v>
       </c>
       <c r="D42" s="19"/>
       <c r="E42" s="2" t="s">
-        <v>2306</v>
+        <v>2307</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="5"/>
       <c r="B43" s="6" t="s">
-        <v>2372</v>
+        <v>2373</v>
       </c>
       <c r="C43" s="7" t="s">
-        <v>2373</v>
+        <v>2374</v>
       </c>
       <c r="D43" s="19"/>
       <c r="E43" s="2" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="5"/>
       <c r="B44" s="6" t="s">
-        <v>2374</v>
+        <v>2375</v>
       </c>
       <c r="C44" s="7" t="s">
-        <v>2375</v>
+        <v>2376</v>
       </c>
       <c r="D44" s="19"/>
       <c r="E44" s="2" t="s">
-        <v>2308</v>
+        <v>2309</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="5"/>
       <c r="B45" s="6" t="s">
-        <v>2376</v>
+        <v>2377</v>
       </c>
       <c r="C45" s="7" t="s">
-        <v>2377</v>
+        <v>2378</v>
       </c>
       <c r="D45" s="19"/>
       <c r="E45" s="2" t="s">
-        <v>2310</v>
+        <v>2311</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="5"/>
       <c r="B46" s="6" t="s">
-        <v>2378</v>
+        <v>2379</v>
       </c>
       <c r="C46" s="7" t="s">
-        <v>2379</v>
+        <v>2380</v>
       </c>
       <c r="D46" s="19"/>
       <c r="E46" s="2" t="s">
-        <v>2312</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="5"/>
       <c r="B47" s="6" t="s">
-        <v>2380</v>
+        <v>2381</v>
       </c>
       <c r="C47" s="7" t="s">
-        <v>2381</v>
+        <v>2382</v>
       </c>
       <c r="D47" s="19"/>
       <c r="E47" s="2" t="s">
-        <v>2312</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="5"/>
       <c r="B48" s="6" t="s">
-        <v>2382</v>
+        <v>2383</v>
       </c>
       <c r="C48" s="7" t="s">
-        <v>2383</v>
+        <v>2384</v>
       </c>
       <c r="D48" s="19"/>
       <c r="E48" s="2" t="s">
-        <v>2312</v>
+        <v>2313</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="5"/>
       <c r="B49" s="6" t="s">
-        <v>2384</v>
+        <v>2385</v>
       </c>
       <c r="C49" s="7" t="s">
-        <v>2385</v>
+        <v>2386</v>
       </c>
       <c r="D49" s="19"/>
       <c r="E49" s="2" t="s">
-        <v>2314</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="5"/>
       <c r="B50" s="6" t="s">
-        <v>2386</v>
+        <v>2387</v>
       </c>
       <c r="C50" s="7" t="s">
-        <v>2387</v>
+        <v>2388</v>
       </c>
       <c r="D50" s="19"/>
       <c r="E50" s="2" t="s">
-        <v>2314</v>
+        <v>2315</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="5"/>
       <c r="B51" s="6" t="s">
-        <v>2388</v>
+        <v>2389</v>
       </c>
       <c r="C51" s="7" t="s">
-        <v>2389</v>
+        <v>2390</v>
       </c>
       <c r="D51" s="19"/>
       <c r="E51" s="2" t="s">
-        <v>2316</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="5"/>
       <c r="B52" s="6" t="s">
-        <v>2390</v>
+        <v>2391</v>
       </c>
       <c r="C52" s="7" t="s">
-        <v>2391</v>
+        <v>2392</v>
       </c>
       <c r="D52" s="19"/>
       <c r="E52" s="2" t="s">
-        <v>2316</v>
+        <v>2317</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="5"/>
       <c r="B53" s="6" t="s">
-        <v>2392</v>
+        <v>2393</v>
       </c>
       <c r="C53" s="7" t="s">
-        <v>2393</v>
+        <v>2394</v>
       </c>
       <c r="D53" s="19"/>
       <c r="E53" s="2" t="s">
-        <v>2318</v>
+        <v>2319</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="5"/>
       <c r="B54" s="6" t="s">
-        <v>2394</v>
+        <v>2395</v>
       </c>
       <c r="C54" s="7" t="s">
-        <v>2395</v>
+        <v>2396</v>
       </c>
       <c r="D54" s="19"/>
       <c r="E54" s="2" t="s">
-        <v>2320</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="5"/>
       <c r="B55" s="6" t="s">
-        <v>2396</v>
+        <v>2397</v>
       </c>
       <c r="C55" s="7" t="s">
-        <v>2397</v>
+        <v>2398</v>
       </c>
       <c r="D55" s="19"/>
       <c r="E55" s="2" t="s">
-        <v>2320</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="5"/>
       <c r="B56" s="6" t="s">
-        <v>2398</v>
+        <v>2399</v>
       </c>
       <c r="C56" s="7" t="s">
-        <v>2399</v>
+        <v>2400</v>
       </c>
       <c r="D56" s="19"/>
       <c r="E56" s="2" t="s">
-        <v>2320</v>
+        <v>2321</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="5"/>
       <c r="B57" s="6" t="s">
-        <v>2400</v>
+        <v>2401</v>
       </c>
       <c r="C57" s="7" t="s">
-        <v>2401</v>
+        <v>2402</v>
       </c>
       <c r="D57" s="19"/>
       <c r="E57" s="2" t="s">
-        <v>2322</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="5"/>
       <c r="B58" s="6" t="s">
-        <v>2402</v>
+        <v>2403</v>
       </c>
       <c r="C58" s="7" t="s">
-        <v>2403</v>
+        <v>2404</v>
       </c>
       <c r="D58" s="19"/>
       <c r="E58" s="2" t="s">
-        <v>2322</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="5"/>
       <c r="B59" s="6" t="s">
-        <v>2404</v>
+        <v>2405</v>
       </c>
       <c r="C59" s="7" t="s">
-        <v>2405</v>
+        <v>2406</v>
       </c>
       <c r="D59" s="19"/>
       <c r="E59" s="2" t="s">
-        <v>2322</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="60" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="5"/>
       <c r="B60" s="6" t="s">
-        <v>2406</v>
+        <v>2407</v>
       </c>
       <c r="C60" s="7" t="s">
-        <v>2407</v>
+        <v>2408</v>
       </c>
       <c r="D60" s="19"/>
       <c r="E60" s="2" t="s">
-        <v>2322</v>
+        <v>2323</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A61" s="5"/>
       <c r="B61" s="6" t="s">
-        <v>2408</v>
+        <v>2409</v>
       </c>
       <c r="C61" s="7" t="s">
-        <v>2409</v>
+        <v>2410</v>
       </c>
       <c r="D61" s="19"/>
       <c r="E61" s="2" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="62" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="5"/>
       <c r="B62" s="6" t="s">
-        <v>2410</v>
+        <v>2411</v>
       </c>
       <c r="C62" s="7" t="s">
-        <v>2411</v>
+        <v>2412</v>
       </c>
       <c r="D62" s="19"/>
       <c r="E62" s="2" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A63" s="5"/>
       <c r="B63" s="6" t="s">
-        <v>2412</v>
+        <v>2413</v>
       </c>
       <c r="C63" s="7" t="s">
-        <v>2413</v>
+        <v>2414</v>
       </c>
       <c r="D63" s="19"/>
       <c r="E63" s="2" t="s">
-        <v>2324</v>
+        <v>2325</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A64" s="5"/>
       <c r="B64" s="6" t="s">
-        <v>2414</v>
+        <v>2415</v>
       </c>
       <c r="C64" s="7" t="s">
-        <v>2415</v>
+        <v>2416</v>
       </c>
       <c r="D64" s="19"/>
       <c r="E64" s="2" t="s">
-        <v>2326</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="65" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A65" s="5"/>
       <c r="B65" s="6" t="s">
-        <v>2416</v>
+        <v>2417</v>
       </c>
       <c r="C65" s="7" t="s">
-        <v>2417</v>
+        <v>2418</v>
       </c>
       <c r="D65" s="19"/>
       <c r="E65" s="2" t="s">
-        <v>2326</v>
+        <v>2327</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A66" s="5"/>
       <c r="B66" s="6" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
       <c r="C66" s="7" t="s">
-        <v>2419</v>
+        <v>2420</v>
       </c>
       <c r="D66" s="19"/>
       <c r="E66" s="2" t="s">
-        <v>2332</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="67" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A67" s="5"/>
       <c r="B67" s="6" t="s">
-        <v>2420</v>
+        <v>2421</v>
       </c>
       <c r="C67" s="7" t="s">
-        <v>2421</v>
+        <v>2422</v>
       </c>
       <c r="D67" s="19"/>
       <c r="E67" s="2" t="s">
-        <v>2332</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A68" s="5"/>
       <c r="B68" s="6" t="s">
-        <v>2422</v>
+        <v>2423</v>
       </c>
       <c r="C68" s="7" t="s">
-        <v>2423</v>
+        <v>2424</v>
       </c>
       <c r="D68" s="19"/>
       <c r="E68" s="2" t="s">
-        <v>2332</v>
+        <v>2333</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A69" s="5"/>
       <c r="B69" s="6" t="s">
-        <v>2424</v>
+        <v>2425</v>
       </c>
       <c r="C69" s="7" t="s">
-        <v>2425</v>
+        <v>2426</v>
       </c>
       <c r="D69" s="19"/>
       <c r="E69" s="2" t="s">
-        <v>2348</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A70" s="5"/>
       <c r="B70" s="6" t="s">
-        <v>2426</v>
+        <v>2427</v>
       </c>
       <c r="C70" s="7" t="s">
-        <v>2427</v>
+        <v>2428</v>
       </c>
       <c r="D70" s="19"/>
       <c r="E70" s="2" t="s">
-        <v>2348</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A71" s="5"/>
       <c r="B71" s="6" t="s">
-        <v>2428</v>
+        <v>2429</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>2429</v>
+        <v>2430</v>
       </c>
       <c r="D71" s="19"/>
       <c r="E71" s="2" t="s">
-        <v>2348</v>
+        <v>2349</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A72" s="5"/>
       <c r="B72" s="6" t="s">
-        <v>2430</v>
+        <v>2431</v>
       </c>
       <c r="C72" s="7" t="s">
-        <v>2431</v>
+        <v>2432</v>
       </c>
       <c r="D72" s="19"/>
       <c r="E72" s="2" t="s">
-        <v>2350</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A73" s="5"/>
       <c r="B73" s="6" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
       <c r="C73" s="7" t="s">
-        <v>2433</v>
+        <v>2434</v>
       </c>
       <c r="D73" s="19"/>
       <c r="E73" s="2" t="s">
-        <v>2350</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A74" s="5"/>
       <c r="B74" s="6" t="s">
-        <v>2434</v>
+        <v>2435</v>
       </c>
       <c r="C74" s="7" t="s">
-        <v>2435</v>
+        <v>2436</v>
       </c>
       <c r="D74" s="19"/>
       <c r="E74" s="2" t="s">
-        <v>2350</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A75" s="5"/>
       <c r="B75" s="6" t="s">
-        <v>2436</v>
+        <v>2437</v>
       </c>
       <c r="C75" s="7" t="s">
-        <v>2437</v>
+        <v>2438</v>
       </c>
       <c r="D75" s="19"/>
       <c r="E75" s="2" t="s">
-        <v>2350</v>
+        <v>2351</v>
       </c>
     </row>
     <row r="76" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A76" s="5"/>
       <c r="B76" s="6" t="s">
-        <v>2438</v>
+        <v>2439</v>
       </c>
       <c r="C76" s="7" t="s">
-        <v>2439</v>
+        <v>2440</v>
       </c>
       <c r="D76" s="19"/>
       <c r="E76" s="2" t="s">
-        <v>2352</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A77" s="5"/>
       <c r="B77" s="6" t="s">
-        <v>2440</v>
+        <v>2441</v>
       </c>
       <c r="C77" s="7" t="s">
-        <v>2441</v>
+        <v>2442</v>
       </c>
       <c r="D77" s="19"/>
       <c r="E77" s="2" t="s">
-        <v>2352</v>
+        <v>2353</v>
       </c>
     </row>
     <row r="78" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A78" s="5"/>
       <c r="B78" s="6" t="s">
-        <v>2442</v>
+        <v>2443</v>
       </c>
       <c r="C78" s="7" t="s">
-        <v>2443</v>
+        <v>2444</v>
       </c>
       <c r="D78" s="19"/>
       <c r="E78" s="2" t="s">
-        <v>2354</v>
+        <v>2355</v>
       </c>
     </row>
     <row r="79" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A79" s="5"/>
       <c r="B79" s="6" t="s">
-        <v>2444</v>
+        <v>2445</v>
       </c>
       <c r="C79" s="7" t="s">
-        <v>2445</v>
+        <v>2446</v>
       </c>
       <c r="D79" s="19"/>
       <c r="E79" s="2" t="s">
-        <v>2356</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A80" s="5"/>
       <c r="B80" s="6" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
       <c r="C80" s="7" t="s">
-        <v>2447</v>
+        <v>2448</v>
       </c>
       <c r="D80" s="19"/>
       <c r="E80" s="2" t="s">
-        <v>2356</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A81" s="5"/>
       <c r="B81" s="6" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
       <c r="C81" s="7" t="s">
-        <v>2449</v>
+        <v>2450</v>
       </c>
       <c r="D81" s="19"/>
       <c r="E81" s="2" t="s">
-        <v>2356</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A82" s="5"/>
       <c r="B82" s="6" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
       <c r="C82" s="7" t="s">
-        <v>2451</v>
+        <v>2452</v>
       </c>
       <c r="D82" s="19"/>
       <c r="E82" s="2" t="s">
-        <v>2356</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A83" s="5"/>
       <c r="B83" s="6" t="s">
-        <v>2452</v>
+        <v>2453</v>
       </c>
       <c r="C83" s="7" t="s">
-        <v>2453</v>
+        <v>2454</v>
       </c>
       <c r="D83" s="19"/>
       <c r="E83" s="2" t="s">
-        <v>2356</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A84" s="5"/>
       <c r="B84" s="6" t="s">
-        <v>2454</v>
+        <v>2455</v>
       </c>
       <c r="C84" s="7" t="s">
-        <v>2455</v>
+        <v>2456</v>
       </c>
       <c r="D84" s="19"/>
       <c r="E84" s="2" t="s">
-        <v>2356</v>
+        <v>2357</v>
       </c>
     </row>
     <row r="85" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A85" s="5"/>
       <c r="B85" s="6" t="s">
-        <v>2456</v>
+        <v>2457</v>
       </c>
       <c r="C85" s="7" t="s">
-        <v>2457</v>
+        <v>2458</v>
       </c>
       <c r="D85" s="19"/>
       <c r="E85" s="2" t="s">
-        <v>2366</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A86" s="5"/>
       <c r="B86" s="6" t="s">
-        <v>2458</v>
+        <v>2459</v>
       </c>
       <c r="C86" s="7" t="s">
-        <v>2459</v>
+        <v>2460</v>
       </c>
       <c r="D86" s="19"/>
       <c r="E86" s="2" t="s">
-        <v>2366</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="87" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A87" s="5"/>
       <c r="B87" s="6" t="s">
-        <v>2460</v>
+        <v>2461</v>
       </c>
       <c r="C87" s="7" t="s">
-        <v>2461</v>
+        <v>2462</v>
       </c>
       <c r="D87" s="19"/>
       <c r="E87" s="2" t="s">
-        <v>2366</v>
+        <v>2367</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A88" s="5"/>
       <c r="B88" s="6" t="s">
-        <v>2462</v>
+        <v>2463</v>
       </c>
       <c r="C88" s="7" t="s">
-        <v>2463</v>
+        <v>2464</v>
       </c>
       <c r="D88" s="19"/>
       <c r="E88" s="2" t="s">
-        <v>2370</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A89" s="5"/>
       <c r="B89" s="6" t="s">
-        <v>2464</v>
+        <v>2465</v>
       </c>
       <c r="C89" s="7" t="s">
-        <v>2465</v>
+        <v>2466</v>
       </c>
       <c r="D89" s="19"/>
       <c r="E89" s="2" t="s">
-        <v>2370</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A90" s="5"/>
       <c r="B90" s="6" t="s">
-        <v>2466</v>
+        <v>2467</v>
       </c>
       <c r="C90" s="7" t="s">
-        <v>2467</v>
+        <v>2468</v>
       </c>
       <c r="D90" s="19"/>
       <c r="E90" s="2" t="s">
-        <v>2370</v>
+        <v>2371</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A91" s="5"/>
       <c r="B91" s="6" t="s">
-        <v>2468</v>
+        <v>2469</v>
       </c>
       <c r="C91" s="7" t="s">
-        <v>2469</v>
+        <v>2470</v>
       </c>
       <c r="D91" s="21" t="s">
-        <v>2470</v>
+        <v>2471</v>
       </c>
       <c r="E91" s="2" t="s">
-        <v>2372</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A92" s="5"/>
       <c r="B92" s="6" t="s">
-        <v>2471</v>
+        <v>2472</v>
       </c>
       <c r="C92" s="7" t="s">
-        <v>2472</v>
+        <v>2473</v>
       </c>
       <c r="D92" s="21" t="s">
-        <v>2473</v>
+        <v>2474</v>
       </c>
       <c r="E92" s="2" t="s">
-        <v>2372</v>
+        <v>2373</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A93" s="5"/>
       <c r="B93" s="6" t="s">
-        <v>2474</v>
+        <v>2475</v>
       </c>
       <c r="C93" s="7" t="s">
-        <v>2475</v>
+        <v>2476</v>
       </c>
       <c r="D93" s="21" t="s">
-        <v>2476</v>
+        <v>2477</v>
       </c>
       <c r="E93" s="2" t="s">
-        <v>2374</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="94" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A94" s="5"/>
       <c r="B94" s="6" t="s">
-        <v>2477</v>
+        <v>2478</v>
       </c>
       <c r="C94" s="7" t="s">
-        <v>2478</v>
+        <v>2479</v>
       </c>
       <c r="D94" s="21" t="s">
-        <v>2479</v>
+        <v>2480</v>
       </c>
       <c r="E94" s="2" t="s">
-        <v>2374</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="95" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A95" s="5"/>
       <c r="B95" s="6" t="s">
-        <v>2480</v>
+        <v>2481</v>
       </c>
       <c r="C95" s="7" t="s">
-        <v>2481</v>
+        <v>2482</v>
       </c>
       <c r="D95" s="21" t="s">
-        <v>2482</v>
+        <v>2483</v>
       </c>
       <c r="E95" s="2" t="s">
-        <v>2374</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="96" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A96" s="5"/>
       <c r="B96" s="6" t="s">
-        <v>2483</v>
+        <v>2484</v>
       </c>
       <c r="C96" s="7" t="s">
-        <v>2484</v>
+        <v>2485</v>
       </c>
       <c r="D96" s="21" t="s">
-        <v>2485</v>
+        <v>2486</v>
       </c>
       <c r="E96" s="2" t="s">
-        <v>2374</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="97" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A97" s="5"/>
       <c r="B97" s="6" t="s">
-        <v>2486</v>
+        <v>2487</v>
       </c>
       <c r="C97" s="7" t="s">
-        <v>2487</v>
+        <v>2488</v>
       </c>
       <c r="D97" s="21" t="s">
-        <v>2488</v>
+        <v>2489</v>
       </c>
       <c r="E97" s="2" t="s">
-        <v>2374</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="98" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A98" s="5"/>
       <c r="B98" s="6" t="s">
-        <v>2489</v>
+        <v>2490</v>
       </c>
       <c r="C98" s="7" t="s">
-        <v>2490</v>
+        <v>2491</v>
       </c>
       <c r="D98" s="21" t="s">
-        <v>2491</v>
+        <v>2492</v>
       </c>
       <c r="E98" s="2" t="s">
-        <v>2374</v>
+        <v>2375</v>
       </c>
     </row>
     <row r="99" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A99" s="5"/>
       <c r="B99" s="6" t="s">
-        <v>2492</v>
+        <v>2493</v>
       </c>
       <c r="C99" s="7" t="s">
-        <v>2493</v>
+        <v>2494</v>
       </c>
       <c r="D99" s="21" t="s">
-        <v>2494</v>
+        <v>2495</v>
       </c>
       <c r="E99" s="2" t="s">
-        <v>2376</v>
+        <v>2377</v>
       </c>
     </row>
     <row r="100" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A100" s="5"/>
       <c r="B100" s="6" t="s">
-        <v>2495</v>
+        <v>2496</v>
       </c>
       <c r="C100" s="7" t="s">
-        <v>2496</v>
+        <v>2497</v>
       </c>
       <c r="D100" s="21" t="s">
-        <v>2497</v>
+        <v>2498</v>
       </c>
       <c r="E100" s="2" t="s">
-        <v>2378</v>
+        <v>2379</v>
       </c>
     </row>
     <row r="101" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A101" s="5"/>
       <c r="B101" s="6" t="s">
-        <v>2498</v>
+        <v>2499</v>
       </c>
       <c r="C101" s="7" t="s">
-        <v>2499</v>
+        <v>2500</v>
       </c>
       <c r="D101" s="21" t="s">
-        <v>2500</v>
+        <v>2501</v>
       </c>
       <c r="E101" s="2" t="s">
-        <v>2380</v>
+        <v>2381</v>
       </c>
     </row>
     <row r="102" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A102" s="5"/>
       <c r="B102" s="6" t="s">
-        <v>2501</v>
+        <v>2502</v>
       </c>
       <c r="C102" s="7" t="s">
-        <v>2502</v>
+        <v>2503</v>
       </c>
       <c r="D102" s="21" t="s">
-        <v>2503</v>
+        <v>2504</v>
       </c>
       <c r="E102" s="2" t="s">
-        <v>2382</v>
+        <v>2383</v>
       </c>
     </row>
     <row r="103" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A103" s="5"/>
       <c r="B103" s="6" t="s">
-        <v>2504</v>
+        <v>2505</v>
       </c>
       <c r="C103" s="7" t="s">
-        <v>2505</v>
+        <v>2506</v>
       </c>
       <c r="D103" s="21" t="s">
-        <v>2506</v>
+        <v>2507</v>
       </c>
       <c r="E103" s="2" t="s">
-        <v>2384</v>
+        <v>2385</v>
       </c>
     </row>
     <row r="104" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A104" s="5"/>
       <c r="B104" s="6" t="s">
-        <v>2507</v>
+        <v>2508</v>
       </c>
       <c r="C104" s="7" t="s">
-        <v>2508</v>
+        <v>2509</v>
       </c>
       <c r="D104" s="21" t="s">
-        <v>2509</v>
+        <v>2510</v>
       </c>
       <c r="E104" s="2" t="s">
-        <v>2386</v>
+        <v>2387</v>
       </c>
     </row>
     <row r="105" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A105" s="5"/>
       <c r="B105" s="6" t="s">
-        <v>2510</v>
+        <v>2511</v>
       </c>
       <c r="C105" s="7" t="s">
-        <v>2511</v>
+        <v>2512</v>
       </c>
       <c r="D105" s="21" t="s">
-        <v>2512</v>
+        <v>2513</v>
       </c>
       <c r="E105" s="2" t="s">
-        <v>2388</v>
+        <v>2389</v>
       </c>
     </row>
     <row r="106" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A106" s="5"/>
       <c r="B106" s="6" t="s">
-        <v>2513</v>
+        <v>2514</v>
       </c>
       <c r="C106" s="7" t="s">
-        <v>2514</v>
+        <v>2515</v>
       </c>
       <c r="D106" s="21" t="s">
-        <v>2515</v>
+        <v>2516</v>
       </c>
       <c r="E106" s="2" t="s">
-        <v>2390</v>
+        <v>2391</v>
       </c>
     </row>
     <row r="107" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A107" s="5"/>
       <c r="B107" s="6" t="s">
-        <v>2516</v>
+        <v>2517</v>
       </c>
       <c r="C107" s="7" t="s">
-        <v>2517</v>
+        <v>2518</v>
       </c>
       <c r="D107" s="21" t="s">
-        <v>2518</v>
+        <v>2519</v>
       </c>
       <c r="E107" s="2" t="s">
-        <v>2392</v>
+        <v>2393</v>
       </c>
     </row>
     <row r="108" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A108" s="5"/>
       <c r="B108" s="6" t="s">
-        <v>2519</v>
+        <v>2520</v>
       </c>
       <c r="C108" s="7" t="s">
-        <v>2520</v>
+        <v>2521</v>
       </c>
       <c r="D108" s="21" t="s">
-        <v>2521</v>
+        <v>2522</v>
       </c>
       <c r="E108" s="2" t="s">
-        <v>2394</v>
+        <v>2395</v>
       </c>
     </row>
     <row r="109" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A109" s="5"/>
       <c r="B109" s="6" t="s">
-        <v>2522</v>
+        <v>2523</v>
       </c>
       <c r="C109" s="7" t="s">
-        <v>2523</v>
+        <v>2524</v>
       </c>
       <c r="D109" s="21" t="s">
-        <v>2524</v>
+        <v>2525</v>
       </c>
       <c r="E109" s="2" t="s">
-        <v>2396</v>
+        <v>2397</v>
       </c>
     </row>
     <row r="110" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A110" s="5"/>
       <c r="B110" s="6" t="s">
-        <v>2525</v>
+        <v>2526</v>
       </c>
       <c r="C110" s="7" t="s">
-        <v>2526</v>
+        <v>2527</v>
       </c>
       <c r="D110" s="21" t="s">
-        <v>2527</v>
+        <v>2528</v>
       </c>
       <c r="E110" s="2" t="s">
-        <v>2398</v>
+        <v>2399</v>
       </c>
     </row>
     <row r="111" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A111" s="5"/>
       <c r="B111" s="6" t="s">
-        <v>2528</v>
+        <v>2529</v>
       </c>
       <c r="C111" s="7" t="s">
-        <v>2529</v>
+        <v>2530</v>
       </c>
       <c r="D111" s="21" t="s">
-        <v>2530</v>
+        <v>2531</v>
       </c>
       <c r="E111" s="2" t="s">
-        <v>2400</v>
+        <v>2401</v>
       </c>
     </row>
     <row r="112" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A112" s="5"/>
       <c r="B112" s="6" t="s">
-        <v>2531</v>
+        <v>2532</v>
       </c>
       <c r="C112" s="7" t="s">
-        <v>2532</v>
+        <v>2533</v>
       </c>
       <c r="D112" s="21" t="s">
-        <v>2533</v>
+        <v>2534</v>
       </c>
       <c r="E112" s="2" t="s">
-        <v>2402</v>
+        <v>2403</v>
       </c>
     </row>
     <row r="113" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A113" s="5"/>
       <c r="B113" s="6" t="s">
-        <v>2534</v>
+        <v>2535</v>
       </c>
       <c r="C113" s="7" t="s">
-        <v>2535</v>
+        <v>2536</v>
       </c>
       <c r="D113" s="21" t="s">
-        <v>2536</v>
+        <v>2537</v>
       </c>
       <c r="E113" s="2" t="s">
-        <v>2404</v>
+        <v>2405</v>
       </c>
     </row>
     <row r="114" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A114" s="5"/>
       <c r="B114" s="6" t="s">
-        <v>2537</v>
+        <v>2538</v>
       </c>
       <c r="C114" s="7" t="s">
-        <v>2538</v>
+        <v>2539</v>
       </c>
       <c r="D114" s="21" t="s">
-        <v>2539</v>
+        <v>2540</v>
       </c>
       <c r="E114" s="2" t="s">
-        <v>2406</v>
+        <v>2407</v>
       </c>
     </row>
     <row r="115" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A115" s="5"/>
       <c r="B115" s="6" t="s">
-        <v>2540</v>
+        <v>2541</v>
       </c>
       <c r="C115" s="7" t="s">
-        <v>2541</v>
+        <v>2542</v>
       </c>
       <c r="D115" s="21" t="s">
-        <v>2542</v>
+        <v>2543</v>
       </c>
       <c r="E115" s="2" t="s">
-        <v>2408</v>
+        <v>2409</v>
       </c>
     </row>
     <row r="116" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A116" s="5"/>
       <c r="B116" s="6" t="s">
-        <v>2543</v>
+        <v>2544</v>
       </c>
       <c r="C116" s="7" t="s">
-        <v>2544</v>
+        <v>2545</v>
       </c>
       <c r="D116" s="21" t="s">
-        <v>2545</v>
+        <v>2546</v>
       </c>
       <c r="E116" s="2" t="s">
-        <v>2410</v>
+        <v>2411</v>
       </c>
     </row>
     <row r="117" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A117" s="5"/>
       <c r="B117" s="6" t="s">
-        <v>2546</v>
+        <v>2547</v>
       </c>
       <c r="C117" s="7" t="s">
-        <v>2547</v>
+        <v>2548</v>
       </c>
       <c r="D117" s="21" t="s">
-        <v>2548</v>
+        <v>2549</v>
       </c>
       <c r="E117" s="2" t="s">
-        <v>2412</v>
+        <v>2413</v>
       </c>
     </row>
     <row r="118" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A118" s="5"/>
       <c r="B118" s="6" t="s">
-        <v>2549</v>
+        <v>2550</v>
       </c>
       <c r="C118" s="7" t="s">
-        <v>2550</v>
+        <v>2551</v>
       </c>
       <c r="D118" s="21" t="s">
-        <v>2551</v>
+        <v>2552</v>
       </c>
       <c r="E118" s="2" t="s">
-        <v>2414</v>
+        <v>2415</v>
       </c>
     </row>
     <row r="119" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A119" s="5"/>
       <c r="B119" s="6" t="s">
-        <v>2552</v>
+        <v>2553</v>
       </c>
       <c r="C119" s="7" t="s">
-        <v>2553</v>
+        <v>2554</v>
       </c>
       <c r="D119" s="21" t="s">
-        <v>2554</v>
+        <v>2555</v>
       </c>
       <c r="E119" s="2" t="s">
-        <v>2416</v>
+        <v>2417</v>
       </c>
     </row>
     <row r="120" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A120" s="5"/>
       <c r="B120" s="6" t="s">
-        <v>2555</v>
+        <v>2556</v>
       </c>
       <c r="C120" s="7" t="s">
-        <v>2556</v>
+        <v>2557</v>
       </c>
       <c r="D120" s="21" t="s">
-        <v>2557</v>
+        <v>2558</v>
       </c>
       <c r="E120" s="2" t="s">
-        <v>2328</v>
+        <v>2329</v>
       </c>
     </row>
     <row r="121" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A121" s="5"/>
       <c r="B121" s="6" t="s">
-        <v>2558</v>
+        <v>2559</v>
       </c>
       <c r="C121" s="7" t="s">
-        <v>2559</v>
+        <v>2560</v>
       </c>
       <c r="D121" s="21" t="s">
-        <v>2560</v>
+        <v>2561</v>
       </c>
       <c r="E121" s="2" t="s">
-        <v>2330</v>
+        <v>2331</v>
       </c>
     </row>
     <row r="122" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A122" s="5"/>
       <c r="B122" s="6" t="s">
-        <v>2561</v>
+        <v>2562</v>
       </c>
       <c r="C122" s="7" t="s">
-        <v>2562</v>
+        <v>2563</v>
       </c>
       <c r="D122" s="21" t="s">
-        <v>2563</v>
+        <v>2564</v>
       </c>
       <c r="E122" s="2" t="s">
-        <v>2418</v>
+        <v>2419</v>
       </c>
     </row>
     <row r="123" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A123" s="5"/>
       <c r="B123" s="6" t="s">
-        <v>2564</v>
+        <v>2565</v>
       </c>
       <c r="C123" s="7" t="s">
-        <v>2565</v>
+        <v>2566</v>
       </c>
       <c r="D123" s="21" t="s">
-        <v>2566</v>
+        <v>2567</v>
       </c>
       <c r="E123" s="2" t="s">
-        <v>2420</v>
+        <v>2421</v>
       </c>
     </row>
     <row r="124" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A124" s="5"/>
       <c r="B124" s="6" t="s">
-        <v>2567</v>
+        <v>2568</v>
       </c>
       <c r="C124" s="7" t="s">
-        <v>2568</v>
+        <v>2569</v>
       </c>
       <c r="D124" s="21" t="s">
-        <v>2569</v>
+        <v>2570</v>
       </c>
       <c r="E124" s="2" t="s">
-        <v>2422</v>
+        <v>2423</v>
       </c>
     </row>
     <row r="125" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A125" s="5"/>
       <c r="B125" s="6" t="s">
-        <v>2570</v>
+        <v>2571</v>
       </c>
       <c r="C125" s="7" t="s">
-        <v>2571</v>
+        <v>2572</v>
       </c>
       <c r="D125" s="21" t="s">
-        <v>2572</v>
+        <v>2573</v>
       </c>
       <c r="E125" s="2" t="s">
-        <v>2334</v>
+        <v>2335</v>
       </c>
     </row>
     <row r="126" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A126" s="5"/>
       <c r="B126" s="6" t="s">
-        <v>2573</v>
+        <v>2574</v>
       </c>
       <c r="C126" s="7" t="s">
-        <v>2574</v>
+        <v>2575</v>
       </c>
       <c r="D126" s="21" t="s">
-        <v>2575</v>
+        <v>2576</v>
       </c>
       <c r="E126" s="2" t="s">
-        <v>2336</v>
+        <v>2337</v>
       </c>
     </row>
     <row r="127" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A127" s="5"/>
       <c r="B127" s="6" t="s">
-        <v>2576</v>
+        <v>2577</v>
       </c>
       <c r="C127" s="7" t="s">
-        <v>2577</v>
+        <v>2578</v>
       </c>
       <c r="D127" s="21" t="s">
-        <v>2578</v>
+        <v>2579</v>
       </c>
       <c r="E127" s="2" t="s">
-        <v>2338</v>
+        <v>2339</v>
       </c>
     </row>
     <row r="128" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A128" s="5"/>
       <c r="B128" s="6" t="s">
-        <v>2579</v>
+        <v>2580</v>
       </c>
       <c r="C128" s="7" t="s">
-        <v>2580</v>
+        <v>2581</v>
       </c>
       <c r="D128" s="21" t="s">
-        <v>2581</v>
+        <v>2582</v>
       </c>
       <c r="E128" s="2" t="s">
-        <v>2340</v>
+        <v>2341</v>
       </c>
     </row>
     <row r="129" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A129" s="5"/>
       <c r="B129" s="6" t="s">
-        <v>2582</v>
+        <v>2583</v>
       </c>
       <c r="C129" s="7" t="s">
-        <v>2583</v>
+        <v>2584</v>
       </c>
       <c r="D129" s="21" t="s">
-        <v>2584</v>
+        <v>2585</v>
       </c>
       <c r="E129" s="2" t="s">
-        <v>2342</v>
+        <v>2343</v>
       </c>
     </row>
     <row r="130" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A130" s="5"/>
       <c r="B130" s="6" t="s">
-        <v>2585</v>
+        <v>2586</v>
       </c>
       <c r="C130" s="7" t="s">
-        <v>2586</v>
+        <v>2587</v>
       </c>
       <c r="D130" s="21" t="s">
-        <v>2587</v>
+        <v>2588</v>
       </c>
       <c r="E130" s="2" t="s">
-        <v>2344</v>
+        <v>2345</v>
       </c>
     </row>
     <row r="131" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A131" s="5"/>
       <c r="B131" s="6" t="s">
-        <v>2588</v>
+        <v>2589</v>
       </c>
       <c r="C131" s="7" t="s">
-        <v>2589</v>
+        <v>2590</v>
       </c>
       <c r="D131" s="21" t="s">
-        <v>2590</v>
+        <v>2591</v>
       </c>
       <c r="E131" s="2" t="s">
-        <v>2346</v>
+        <v>2347</v>
       </c>
     </row>
     <row r="132" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A132" s="5"/>
       <c r="B132" s="6" t="s">
-        <v>2591</v>
+        <v>2592</v>
       </c>
       <c r="C132" s="7" t="s">
-        <v>2592</v>
+        <v>2593</v>
       </c>
       <c r="D132" s="21" t="s">
-        <v>2593</v>
+        <v>2594</v>
       </c>
       <c r="E132" s="2" t="s">
-        <v>2424</v>
+        <v>2425</v>
       </c>
     </row>
     <row r="133" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A133" s="5"/>
       <c r="B133" s="6" t="s">
-        <v>2594</v>
+        <v>2595</v>
       </c>
       <c r="C133" s="7" t="s">
-        <v>2595</v>
+        <v>2596</v>
       </c>
       <c r="D133" s="21" t="s">
-        <v>2596</v>
+        <v>2597</v>
       </c>
       <c r="E133" s="2" t="s">
-        <v>2426</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="134" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A134" s="5"/>
       <c r="B134" s="6" t="s">
-        <v>2597</v>
+        <v>2598</v>
       </c>
       <c r="C134" s="7" t="s">
-        <v>2598</v>
+        <v>2599</v>
       </c>
       <c r="D134" s="21" t="s">
-        <v>2599</v>
+        <v>2600</v>
       </c>
       <c r="E134" s="2" t="s">
-        <v>2426</v>
+        <v>2427</v>
       </c>
     </row>
     <row r="135" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A135" s="5"/>
       <c r="B135" s="6" t="s">
-        <v>2600</v>
+        <v>2601</v>
       </c>
       <c r="C135" s="7" t="s">
-        <v>2601</v>
+        <v>2602</v>
       </c>
       <c r="D135" s="21" t="s">
-        <v>2602</v>
+        <v>2603</v>
       </c>
       <c r="E135" s="2" t="s">
-        <v>2428</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="136" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A136" s="5"/>
       <c r="B136" s="6" t="s">
-        <v>2603</v>
+        <v>2604</v>
       </c>
       <c r="C136" s="7" t="s">
-        <v>2604</v>
+        <v>2605</v>
       </c>
       <c r="D136" s="21" t="s">
-        <v>2605</v>
+        <v>2606</v>
       </c>
       <c r="E136" s="2" t="s">
-        <v>2428</v>
+        <v>2429</v>
       </c>
     </row>
     <row r="137" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A137" s="5"/>
       <c r="B137" s="6" t="s">
-        <v>2606</v>
+        <v>2607</v>
       </c>
       <c r="C137" s="7" t="s">
-        <v>2607</v>
+        <v>2608</v>
       </c>
       <c r="D137" s="21" t="s">
-        <v>2608</v>
+        <v>2609</v>
       </c>
       <c r="E137" s="2" t="s">
-        <v>2430</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="138" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A138" s="5"/>
       <c r="B138" s="6" t="s">
-        <v>2609</v>
+        <v>2610</v>
       </c>
       <c r="C138" s="7" t="s">
-        <v>2610</v>
+        <v>2611</v>
       </c>
       <c r="D138" s="21" t="s">
-        <v>2611</v>
+        <v>2612</v>
       </c>
       <c r="E138" s="2" t="s">
-        <v>2430</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="139" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A139" s="5"/>
       <c r="B139" s="6" t="s">
-        <v>2612</v>
+        <v>2613</v>
       </c>
       <c r="C139" s="7" t="s">
-        <v>2613</v>
+        <v>2614</v>
       </c>
       <c r="D139" s="21" t="s">
-        <v>2614</v>
+        <v>2615</v>
       </c>
       <c r="E139" s="2" t="s">
-        <v>2430</v>
+        <v>2431</v>
       </c>
     </row>
     <row r="140" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A140" s="5"/>
       <c r="B140" s="6" t="s">
-        <v>2615</v>
+        <v>2616</v>
       </c>
       <c r="C140" s="7" t="s">
-        <v>2616</v>
+        <v>2617</v>
       </c>
       <c r="D140" s="21" t="s">
-        <v>2617</v>
+        <v>2618</v>
       </c>
       <c r="E140" s="2" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="141" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A141" s="5"/>
       <c r="B141" s="6" t="s">
-        <v>2618</v>
+        <v>2619</v>
       </c>
       <c r="C141" s="7" t="s">
-        <v>2619</v>
+        <v>2620</v>
       </c>
       <c r="D141" s="21" t="s">
-        <v>2620</v>
+        <v>2621</v>
       </c>
       <c r="E141" s="2" t="s">
-        <v>2432</v>
+        <v>2433</v>
       </c>
     </row>
     <row r="142" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A142" s="5"/>
       <c r="B142" s="6" t="s">
-        <v>2621</v>
+        <v>2622</v>
       </c>
       <c r="C142" s="7" t="s">
-        <v>2622</v>
+        <v>2623</v>
       </c>
       <c r="D142" s="21" t="s">
-        <v>2623</v>
+        <v>2624</v>
       </c>
       <c r="E142" s="2" t="s">
-        <v>2434</v>
+        <v>2435</v>
       </c>
     </row>
     <row r="143" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A143" s="5"/>
       <c r="B143" s="6" t="s">
-        <v>2624</v>
+        <v>2625</v>
       </c>
       <c r="C143" s="7" t="s">
-        <v>2625</v>
+        <v>2626</v>
       </c>
       <c r="D143" s="21" t="s">
-        <v>2626</v>
+        <v>2627</v>
       </c>
       <c r="E143" s="2" t="s">
-        <v>2436</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="144" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A144" s="5"/>
       <c r="B144" s="6" t="s">
-        <v>2627</v>
+        <v>2628</v>
       </c>
       <c r="C144" s="7" t="s">
-        <v>2628</v>
+        <v>2629</v>
       </c>
       <c r="D144" s="21" t="s">
-        <v>2629</v>
+        <v>2630</v>
       </c>
       <c r="E144" s="2" t="s">
-        <v>2436</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="145" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A145" s="5"/>
       <c r="B145" s="6" t="s">
-        <v>2630</v>
+        <v>2631</v>
       </c>
       <c r="C145" s="7" t="s">
-        <v>2631</v>
+        <v>2632</v>
       </c>
       <c r="D145" s="21" t="s">
-        <v>2632</v>
+        <v>2633</v>
       </c>
       <c r="E145" s="2" t="s">
-        <v>2436</v>
+        <v>2437</v>
       </c>
     </row>
     <row r="146" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A146" s="5"/>
       <c r="B146" s="6" t="s">
-        <v>2633</v>
+        <v>2634</v>
       </c>
       <c r="C146" s="7" t="s">
-        <v>2634</v>
+        <v>2635</v>
       </c>
       <c r="D146" s="21" t="s">
-        <v>2635</v>
+        <v>2636</v>
       </c>
       <c r="E146" s="2" t="s">
-        <v>2438</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="147" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A147" s="5"/>
       <c r="B147" s="6" t="s">
-        <v>2636</v>
+        <v>2637</v>
       </c>
       <c r="C147" s="7" t="s">
-        <v>2637</v>
+        <v>2638</v>
       </c>
       <c r="D147" s="21" t="s">
-        <v>2638</v>
+        <v>2639</v>
       </c>
       <c r="E147" s="2" t="s">
-        <v>2438</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="148" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A148" s="5"/>
       <c r="B148" s="6" t="s">
-        <v>2639</v>
+        <v>2640</v>
       </c>
       <c r="C148" s="7" t="s">
-        <v>2640</v>
+        <v>2641</v>
       </c>
       <c r="D148" s="21" t="s">
-        <v>2641</v>
+        <v>2642</v>
       </c>
       <c r="E148" s="2" t="s">
-        <v>2438</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="149" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A149" s="5"/>
       <c r="B149" s="6" t="s">
-        <v>2642</v>
+        <v>2643</v>
       </c>
       <c r="C149" s="7" t="s">
-        <v>2643</v>
+        <v>2644</v>
       </c>
       <c r="D149" s="21" t="s">
-        <v>2644</v>
+        <v>2645</v>
       </c>
       <c r="E149" s="2" t="s">
-        <v>2438</v>
+        <v>2439</v>
       </c>
     </row>
     <row r="150" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A150" s="5"/>
       <c r="B150" s="6" t="s">
-        <v>2645</v>
+        <v>2646</v>
       </c>
       <c r="C150" s="7" t="s">
-        <v>2646</v>
+        <v>2647</v>
       </c>
       <c r="D150" s="21" t="s">
-        <v>2647</v>
+        <v>2648</v>
       </c>
       <c r="E150" s="2" t="s">
-        <v>2440</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="151" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A151" s="5"/>
       <c r="B151" s="6" t="s">
-        <v>2648</v>
+        <v>2649</v>
       </c>
       <c r="C151" s="7" t="s">
-        <v>2649</v>
+        <v>2650</v>
       </c>
       <c r="D151" s="21" t="s">
-        <v>2650</v>
+        <v>2651</v>
       </c>
       <c r="E151" s="2" t="s">
-        <v>2440</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="152" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A152" s="5"/>
       <c r="B152" s="6" t="s">
-        <v>2651</v>
+        <v>2652</v>
       </c>
       <c r="C152" s="7" t="s">
-        <v>2652</v>
+        <v>2653</v>
       </c>
       <c r="D152" s="21" t="s">
-        <v>2653</v>
+        <v>2654</v>
       </c>
       <c r="E152" s="2" t="s">
-        <v>2440</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="153" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A153" s="5"/>
       <c r="B153" s="6" t="s">
-        <v>2654</v>
+        <v>2655</v>
       </c>
       <c r="C153" s="7" t="s">
-        <v>2655</v>
+        <v>2656</v>
       </c>
       <c r="D153" s="21" t="s">
-        <v>2656</v>
+        <v>2657</v>
       </c>
       <c r="E153" s="2" t="s">
-        <v>2440</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="154" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A154" s="5"/>
       <c r="B154" s="6" t="s">
-        <v>2657</v>
+        <v>2658</v>
       </c>
       <c r="C154" s="7" t="s">
-        <v>2658</v>
+        <v>2659</v>
       </c>
       <c r="D154" s="21" t="s">
-        <v>2659</v>
+        <v>2660</v>
       </c>
       <c r="E154" s="2" t="s">
-        <v>2440</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="155" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A155" s="5"/>
       <c r="B155" s="6" t="s">
-        <v>2660</v>
+        <v>2661</v>
       </c>
       <c r="C155" s="7" t="s">
-        <v>2661</v>
+        <v>2662</v>
       </c>
       <c r="D155" s="21" t="s">
-        <v>2662</v>
+        <v>2663</v>
       </c>
       <c r="E155" s="2" t="s">
-        <v>2440</v>
+        <v>2441</v>
       </c>
     </row>
     <row r="156" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A156" s="5"/>
       <c r="B156" s="6" t="s">
-        <v>2663</v>
+        <v>2664</v>
       </c>
       <c r="C156" s="7" t="s">
-        <v>2664</v>
+        <v>2665</v>
       </c>
       <c r="D156" s="21" t="s">
-        <v>2665</v>
+        <v>2666</v>
       </c>
       <c r="E156" s="2" t="s">
-        <v>2442</v>
+        <v>2443</v>
       </c>
     </row>
     <row r="157" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A157" s="5"/>
       <c r="B157" s="6" t="s">
-        <v>2666</v>
+        <v>2667</v>
       </c>
       <c r="C157" s="7" t="s">
-        <v>2667</v>
+        <v>2668</v>
       </c>
       <c r="D157" s="21" t="s">
-        <v>2668</v>
+        <v>2669</v>
       </c>
       <c r="E157" s="2" t="s">
-        <v>2442</v>
+        <v>2443</v>
       </c>
     </row>
     <row r="158" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="5"/>
       <c r="B158" s="6" t="s">
-        <v>2669</v>
+        <v>2670</v>
       </c>
       <c r="C158" s="7" t="s">
-        <v>2670</v>
+        <v>2671</v>
       </c>
       <c r="D158" s="21" t="s">
-        <v>2671</v>
+        <v>2672</v>
       </c>
       <c r="E158" s="2" t="s">
-        <v>2444</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="159" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="5"/>
       <c r="B159" s="6" t="s">
-        <v>2672</v>
+        <v>2673</v>
       </c>
       <c r="C159" s="7" t="s">
-        <v>2673</v>
+        <v>2674</v>
       </c>
       <c r="D159" s="21" t="s">
-        <v>2674</v>
+        <v>2675</v>
       </c>
       <c r="E159" s="2" t="s">
-        <v>2444</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="160" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="5"/>
       <c r="B160" s="6" t="s">
-        <v>2675</v>
+        <v>2676</v>
       </c>
       <c r="C160" s="7" t="s">
-        <v>2676</v>
+        <v>2677</v>
       </c>
       <c r="D160" s="21" t="s">
-        <v>2677</v>
+        <v>2678</v>
       </c>
       <c r="E160" s="2" t="s">
-        <v>2444</v>
+        <v>2445</v>
       </c>
     </row>
     <row r="161" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="5"/>
       <c r="B161" s="6" t="s">
-        <v>2678</v>
+        <v>2679</v>
       </c>
       <c r="C161" s="7" t="s">
-        <v>2679</v>
+        <v>2680</v>
       </c>
       <c r="D161" s="21" t="s">
-        <v>2680</v>
+        <v>2681</v>
       </c>
       <c r="E161" s="2" t="s">
-        <v>2446</v>
+        <v>2447</v>
       </c>
     </row>
     <row r="162" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="5"/>
       <c r="B162" s="6" t="s">
-        <v>2681</v>
+        <v>2682</v>
       </c>
       <c r="C162" s="7" t="s">
-        <v>2682</v>
+        <v>2683</v>
       </c>
       <c r="D162" s="21" t="s">
-        <v>2683</v>
+        <v>2684</v>
       </c>
       <c r="E162" s="2" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
     </row>
     <row r="163" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="5"/>
       <c r="B163" s="6" t="s">
+        <v>2685</v>
+      </c>
+      <c r="C163" s="7" t="s">
+        <v>2686</v>
+      </c>
+      <c r="D163" s="21" t="s">
         <v>2684</v>
       </c>
-      <c r="C163" s="7" t="s">
-        <v>2685</v>
-      </c>
-      <c r="D163" s="21" t="s">
-        <v>2683</v>
-      </c>
       <c r="E163" s="2" t="s">
-        <v>2448</v>
+        <v>2449</v>
       </c>
     </row>
     <row r="164" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="5"/>
       <c r="B164" s="6" t="s">
-        <v>2686</v>
+        <v>2687</v>
       </c>
       <c r="C164" s="7" t="s">
-        <v>2687</v>
+        <v>2688</v>
       </c>
       <c r="D164" s="21" t="s">
-        <v>2688</v>
+        <v>2689</v>
       </c>
       <c r="E164" s="2" t="s">
-        <v>2450</v>
+        <v>2451</v>
       </c>
     </row>
     <row r="165" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="5"/>
       <c r="B165" s="6" t="s">
-        <v>2689</v>
+        <v>2690</v>
       </c>
       <c r="C165" s="7" t="s">
-        <v>2690</v>
+        <v>2691</v>
       </c>
       <c r="D165" s="21" t="s">
-        <v>2691</v>
+        <v>2692</v>
       </c>
       <c r="E165" s="2" t="s">
-        <v>2452</v>
+        <v>2453</v>
       </c>
     </row>
     <row r="166" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="5"/>
       <c r="B166" s="6" t="s">
-        <v>2692</v>
+        <v>2693</v>
       </c>
       <c r="C166" s="7" t="s">
-        <v>2693</v>
+        <v>2694</v>
       </c>
       <c r="D166" s="21" t="s">
-        <v>2694</v>
+        <v>2695</v>
       </c>
       <c r="E166" s="2" t="s">
-        <v>2454</v>
+        <v>2455</v>
       </c>
     </row>
     <row r="167" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="5"/>
       <c r="B167" s="6" t="s">
-        <v>2695</v>
+        <v>2696</v>
       </c>
       <c r="C167" s="7" t="s">
-        <v>2696</v>
+        <v>2697</v>
       </c>
       <c r="D167" s="21" t="s">
-        <v>2697</v>
+        <v>2698</v>
       </c>
       <c r="E167" s="2" t="s">
-        <v>2358</v>
+        <v>2359</v>
       </c>
     </row>
     <row r="168" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="5"/>
       <c r="B168" s="6" t="s">
-        <v>2698</v>
+        <v>2699</v>
       </c>
       <c r="C168" s="7" t="s">
-        <v>2699</v>
+        <v>2700</v>
       </c>
       <c r="D168" s="21" t="s">
-        <v>2700</v>
+        <v>2701</v>
       </c>
       <c r="E168" s="2" t="s">
-        <v>2360</v>
+        <v>2361</v>
       </c>
     </row>
     <row r="169" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="5"/>
       <c r="B169" s="6" t="s">
-        <v>2701</v>
+        <v>2702</v>
       </c>
       <c r="C169" s="7" t="s">
-        <v>2702</v>
+        <v>2703</v>
       </c>
       <c r="D169" s="21" t="s">
-        <v>2703</v>
+        <v>2704</v>
       </c>
       <c r="E169" s="2" t="s">
-        <v>2362</v>
+        <v>2363</v>
       </c>
     </row>
     <row r="170" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="5"/>
       <c r="B170" s="6" t="s">
-        <v>2704</v>
+        <v>2705</v>
       </c>
       <c r="C170" s="7" t="s">
-        <v>2705</v>
+        <v>2706</v>
       </c>
       <c r="D170" s="21" t="s">
-        <v>2706</v>
+        <v>2707</v>
       </c>
       <c r="E170" s="2" t="s">
-        <v>2364</v>
+        <v>2365</v>
       </c>
     </row>
     <row r="171" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="5"/>
       <c r="B171" s="6" t="s">
-        <v>2707</v>
+        <v>2708</v>
       </c>
       <c r="C171" s="7" t="s">
-        <v>2708</v>
+        <v>2709</v>
       </c>
       <c r="D171" s="21" t="s">
-        <v>2709</v>
+        <v>2710</v>
       </c>
       <c r="E171" s="2" t="s">
-        <v>2456</v>
+        <v>2457</v>
       </c>
     </row>
     <row r="172" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="5"/>
       <c r="B172" s="6" t="s">
-        <v>2710</v>
+        <v>2711</v>
       </c>
       <c r="C172" s="7" t="s">
-        <v>2711</v>
+        <v>2712</v>
       </c>
       <c r="D172" s="21" t="s">
-        <v>2712</v>
+        <v>2713</v>
       </c>
       <c r="E172" s="2" t="s">
-        <v>2458</v>
+        <v>2459</v>
       </c>
     </row>
     <row r="173" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="5"/>
       <c r="B173" s="6" t="s">
-        <v>2713</v>
+        <v>2714</v>
       </c>
       <c r="C173" s="7" t="s">
-        <v>2714</v>
+        <v>2715</v>
       </c>
       <c r="D173" s="21" t="s">
-        <v>2715</v>
+        <v>2716</v>
       </c>
       <c r="E173" s="2" t="s">
-        <v>2460</v>
+        <v>2461</v>
       </c>
     </row>
     <row r="174" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="5"/>
       <c r="B174" s="6" t="s">
-        <v>2716</v>
+        <v>2717</v>
       </c>
       <c r="C174" s="7" t="s">
-        <v>2717</v>
+        <v>2718</v>
       </c>
       <c r="D174" s="21" t="s">
-        <v>2718</v>
+        <v>2719</v>
       </c>
       <c r="E174" s="2" t="s">
-        <v>2368</v>
+        <v>2369</v>
       </c>
     </row>
     <row r="175" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="5"/>
       <c r="B175" s="6" t="s">
-        <v>2719</v>
+        <v>2720</v>
       </c>
       <c r="C175" s="7" t="s">
-        <v>2720</v>
+        <v>2721</v>
       </c>
       <c r="D175" s="21" t="s">
-        <v>2721</v>
+        <v>2722</v>
       </c>
       <c r="E175" s="2" t="s">
-        <v>2462</v>
+        <v>2463</v>
       </c>
     </row>
     <row r="176" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="5"/>
       <c r="B176" s="6" t="s">
-        <v>2722</v>
+        <v>2723</v>
       </c>
       <c r="C176" s="7" t="s">
-        <v>2723</v>
+        <v>2724</v>
       </c>
       <c r="D176" s="21" t="s">
-        <v>2724</v>
+        <v>2725</v>
       </c>
       <c r="E176" s="2" t="s">
-        <v>2464</v>
+        <v>2465</v>
       </c>
     </row>
     <row r="177" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="5"/>
       <c r="B177" s="11" t="s">
-        <v>2725</v>
+        <v>2726</v>
       </c>
       <c r="C177" s="12" t="s">
-        <v>2726</v>
+        <v>2727</v>
       </c>
       <c r="D177" s="21" t="s">
-        <v>2727</v>
+        <v>2728</v>
       </c>
       <c r="E177" s="2" t="s">
-        <v>2466</v>
+        <v>2467</v>
       </c>
     </row>
   </sheetData>
@@ -17941,208 +17944,208 @@
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
-        <v>2310</v>
+        <v>2311</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>2728</v>
+        <v>2729</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>2729</v>
+        <v>2730</v>
       </c>
       <c r="E2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5"/>
       <c r="B3" s="6" t="s">
-        <v>2312</v>
+        <v>2313</v>
       </c>
       <c r="C3" s="7" t="s">
+        <v>2731</v>
+      </c>
+      <c r="D3" s="21" t="s">
         <v>2730</v>
-      </c>
-      <c r="D3" s="21" t="s">
-        <v>2729</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5"/>
       <c r="B4" s="6" t="s">
-        <v>2731</v>
+        <v>2732</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>2732</v>
+        <v>2733</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>2729</v>
+        <v>2730</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5"/>
       <c r="B5" s="6" t="s">
-        <v>2314</v>
+        <v>2315</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>2733</v>
+        <v>2734</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>2734</v>
+        <v>2735</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
       <c r="B6" s="6" t="s">
-        <v>2316</v>
+        <v>2317</v>
       </c>
       <c r="C6" s="7" t="s">
+        <v>2736</v>
+      </c>
+      <c r="D6" s="21" t="s">
         <v>2735</v>
-      </c>
-      <c r="D6" s="21" t="s">
-        <v>2734</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
       <c r="B7" s="6" t="s">
-        <v>2736</v>
+        <v>2737</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>2737</v>
+        <v>2738</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>2734</v>
+        <v>2735</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5"/>
       <c r="B8" s="6" t="s">
-        <v>2330</v>
+        <v>2331</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>2738</v>
+        <v>2739</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>2739</v>
+        <v>2740</v>
       </c>
       <c r="E8" s="3"/>
     </row>
     <row r="9" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="5"/>
       <c r="B9" s="6" t="s">
-        <v>2332</v>
+        <v>2333</v>
       </c>
       <c r="C9" s="7" t="s">
+        <v>2741</v>
+      </c>
+      <c r="D9" s="21" t="s">
         <v>2740</v>
-      </c>
-      <c r="D9" s="21" t="s">
-        <v>2739</v>
       </c>
       <c r="E9" s="3"/>
     </row>
     <row r="10" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="5"/>
       <c r="B10" s="6" t="s">
-        <v>2334</v>
+        <v>2335</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>2741</v>
+        <v>2742</v>
       </c>
       <c r="D10" s="21" t="s">
-        <v>2739</v>
+        <v>2740</v>
       </c>
       <c r="E10" s="3"/>
     </row>
     <row r="11" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A11" s="5"/>
       <c r="B11" s="6" t="s">
-        <v>2742</v>
+        <v>2743</v>
       </c>
       <c r="C11" s="7" t="s">
-        <v>2743</v>
+        <v>2744</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>2739</v>
+        <v>2740</v>
       </c>
       <c r="E11" s="3"/>
     </row>
     <row r="12" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A12" s="5"/>
       <c r="B12" s="6" t="s">
-        <v>2336</v>
+        <v>2337</v>
       </c>
       <c r="C12" s="7" t="s">
-        <v>2744</v>
+        <v>2745</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>2745</v>
+        <v>2746</v>
       </c>
       <c r="E12" s="3"/>
     </row>
     <row r="13" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A13" s="5"/>
       <c r="B13" s="6" t="s">
-        <v>2338</v>
+        <v>2339</v>
       </c>
       <c r="C13" s="7" t="s">
+        <v>2747</v>
+      </c>
+      <c r="D13" s="21" t="s">
         <v>2746</v>
-      </c>
-      <c r="D13" s="21" t="s">
-        <v>2745</v>
       </c>
       <c r="E13" s="3"/>
     </row>
     <row r="14" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A14" s="5"/>
       <c r="B14" s="6" t="s">
-        <v>2340</v>
+        <v>2341</v>
       </c>
       <c r="C14" s="7" t="s">
-        <v>2747</v>
+        <v>2748</v>
       </c>
       <c r="D14" s="21" t="s">
-        <v>2745</v>
+        <v>2746</v>
       </c>
       <c r="E14" s="3"/>
     </row>
     <row r="15" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A15" s="5"/>
       <c r="B15" s="6" t="s">
-        <v>2342</v>
+        <v>2343</v>
       </c>
       <c r="C15" s="7" t="s">
-        <v>2748</v>
+        <v>2749</v>
       </c>
       <c r="D15" s="21" t="s">
-        <v>2745</v>
+        <v>2746</v>
       </c>
       <c r="E15" s="3"/>
     </row>
     <row r="16" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A16" s="5"/>
       <c r="B16" s="6" t="s">
-        <v>2749</v>
+        <v>2750</v>
       </c>
       <c r="C16" s="7" t="s">
-        <v>2750</v>
+        <v>2751</v>
       </c>
       <c r="D16" s="21" t="s">
-        <v>2745</v>
+        <v>2746</v>
       </c>
       <c r="E16" s="3"/>
     </row>
     <row r="17" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A17" s="5"/>
       <c r="B17" s="11" t="s">
-        <v>2751</v>
+        <v>2752</v>
       </c>
       <c r="C17" s="12" t="s">
-        <v>2752</v>
+        <v>2753</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>2752</v>
+        <v>2753</v>
       </c>
       <c r="E17" s="3"/>
     </row>
@@ -26115,12 +26118,14 @@
       <c r="E156" s="3"/>
     </row>
     <row r="157" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A157" s="5"/>
+      <c r="A157" s="5" t="s">
+        <v>1639</v>
+      </c>
       <c r="B157" s="6" t="s">
-        <v>1639</v>
+        <v>1640</v>
       </c>
       <c r="C157" s="7" t="s">
-        <v>1640</v>
+        <v>1641</v>
       </c>
       <c r="D157" s="19"/>
       <c r="E157" s="3"/>
@@ -26128,10 +26133,10 @@
     <row r="158" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A158" s="5"/>
       <c r="B158" s="6" t="s">
-        <v>1641</v>
+        <v>1642</v>
       </c>
       <c r="C158" s="7" t="s">
-        <v>1642</v>
+        <v>1643</v>
       </c>
       <c r="D158" s="19"/>
       <c r="E158" s="3"/>
@@ -26139,10 +26144,10 @@
     <row r="159" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A159" s="5"/>
       <c r="B159" s="6" t="s">
-        <v>1643</v>
+        <v>1644</v>
       </c>
       <c r="C159" s="7" t="s">
-        <v>1644</v>
+        <v>1645</v>
       </c>
       <c r="D159" s="19"/>
       <c r="E159" s="3"/>
@@ -26150,10 +26155,10 @@
     <row r="160" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A160" s="5"/>
       <c r="B160" s="6" t="s">
-        <v>1645</v>
+        <v>1646</v>
       </c>
       <c r="C160" s="7" t="s">
-        <v>1646</v>
+        <v>1647</v>
       </c>
       <c r="D160" s="19"/>
       <c r="E160" s="3"/>
@@ -26161,10 +26166,10 @@
     <row r="161" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A161" s="5"/>
       <c r="B161" s="6" t="s">
-        <v>1647</v>
+        <v>1648</v>
       </c>
       <c r="C161" s="7" t="s">
-        <v>1648</v>
+        <v>1649</v>
       </c>
       <c r="D161" s="19"/>
       <c r="E161" s="3"/>
@@ -26172,10 +26177,10 @@
     <row r="162" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A162" s="5"/>
       <c r="B162" s="6" t="s">
-        <v>1649</v>
+        <v>1650</v>
       </c>
       <c r="C162" s="7" t="s">
-        <v>1650</v>
+        <v>1651</v>
       </c>
       <c r="D162" s="19"/>
       <c r="E162" s="3"/>
@@ -26183,10 +26188,10 @@
     <row r="163" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A163" s="5"/>
       <c r="B163" s="6" t="s">
-        <v>1651</v>
+        <v>1652</v>
       </c>
       <c r="C163" s="7" t="s">
-        <v>1652</v>
+        <v>1653</v>
       </c>
       <c r="D163" s="19"/>
       <c r="E163" s="3"/>
@@ -26194,10 +26199,10 @@
     <row r="164" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A164" s="5"/>
       <c r="B164" s="6" t="s">
-        <v>1653</v>
+        <v>1654</v>
       </c>
       <c r="C164" s="7" t="s">
-        <v>1654</v>
+        <v>1655</v>
       </c>
       <c r="D164" s="19"/>
       <c r="E164" s="3"/>
@@ -26205,10 +26210,10 @@
     <row r="165" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A165" s="5"/>
       <c r="B165" s="6" t="s">
-        <v>1655</v>
+        <v>1656</v>
       </c>
       <c r="C165" s="7" t="s">
-        <v>1656</v>
+        <v>1657</v>
       </c>
       <c r="D165" s="19"/>
       <c r="E165" s="3"/>
@@ -26216,10 +26221,10 @@
     <row r="166" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A166" s="5"/>
       <c r="B166" s="6" t="s">
-        <v>1657</v>
+        <v>1658</v>
       </c>
       <c r="C166" s="7" t="s">
-        <v>1658</v>
+        <v>1659</v>
       </c>
       <c r="D166" s="19"/>
       <c r="E166" s="3"/>
@@ -26227,10 +26232,10 @@
     <row r="167" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A167" s="5"/>
       <c r="B167" s="6" t="s">
-        <v>1659</v>
+        <v>1660</v>
       </c>
       <c r="C167" s="7" t="s">
-        <v>1660</v>
+        <v>1661</v>
       </c>
       <c r="D167" s="19"/>
       <c r="E167" s="3"/>
@@ -26238,10 +26243,10 @@
     <row r="168" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A168" s="5"/>
       <c r="B168" s="6" t="s">
-        <v>1661</v>
+        <v>1662</v>
       </c>
       <c r="C168" s="7" t="s">
-        <v>1662</v>
+        <v>1663</v>
       </c>
       <c r="D168" s="19"/>
       <c r="E168" s="3"/>
@@ -26249,10 +26254,10 @@
     <row r="169" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A169" s="5"/>
       <c r="B169" s="6" t="s">
-        <v>1663</v>
+        <v>1664</v>
       </c>
       <c r="C169" s="7" t="s">
-        <v>1664</v>
+        <v>1665</v>
       </c>
       <c r="D169" s="19"/>
       <c r="E169" s="3"/>
@@ -26260,10 +26265,10 @@
     <row r="170" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A170" s="5"/>
       <c r="B170" s="6" t="s">
-        <v>1665</v>
+        <v>1666</v>
       </c>
       <c r="C170" s="7" t="s">
-        <v>1666</v>
+        <v>1667</v>
       </c>
       <c r="D170" s="19"/>
       <c r="E170" s="3"/>
@@ -26271,10 +26276,10 @@
     <row r="171" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A171" s="5"/>
       <c r="B171" s="6" t="s">
-        <v>1667</v>
+        <v>1668</v>
       </c>
       <c r="C171" s="7" t="s">
-        <v>1668</v>
+        <v>1669</v>
       </c>
       <c r="D171" s="19"/>
       <c r="E171" s="3"/>
@@ -26282,10 +26287,10 @@
     <row r="172" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A172" s="5"/>
       <c r="B172" s="6" t="s">
-        <v>1669</v>
+        <v>1670</v>
       </c>
       <c r="C172" s="7" t="s">
-        <v>1670</v>
+        <v>1671</v>
       </c>
       <c r="D172" s="19"/>
       <c r="E172" s="3"/>
@@ -26293,10 +26298,10 @@
     <row r="173" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A173" s="5"/>
       <c r="B173" s="6" t="s">
-        <v>1671</v>
+        <v>1672</v>
       </c>
       <c r="C173" s="7" t="s">
-        <v>1672</v>
+        <v>1673</v>
       </c>
       <c r="D173" s="19"/>
       <c r="E173" s="3"/>
@@ -26304,10 +26309,10 @@
     <row r="174" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A174" s="5"/>
       <c r="B174" s="6" t="s">
-        <v>1673</v>
+        <v>1674</v>
       </c>
       <c r="C174" s="7" t="s">
-        <v>1674</v>
+        <v>1675</v>
       </c>
       <c r="D174" s="19"/>
       <c r="E174" s="3"/>
@@ -26315,10 +26320,10 @@
     <row r="175" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A175" s="5"/>
       <c r="B175" s="6" t="s">
-        <v>1675</v>
+        <v>1676</v>
       </c>
       <c r="C175" s="7" t="s">
-        <v>1676</v>
+        <v>1677</v>
       </c>
       <c r="D175" s="19"/>
       <c r="E175" s="3"/>
@@ -26326,10 +26331,10 @@
     <row r="176" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A176" s="5"/>
       <c r="B176" s="6" t="s">
-        <v>1677</v>
+        <v>1678</v>
       </c>
       <c r="C176" s="7" t="s">
-        <v>1678</v>
+        <v>1679</v>
       </c>
       <c r="D176" s="19"/>
       <c r="E176" s="3"/>
@@ -26337,10 +26342,10 @@
     <row r="177" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A177" s="5"/>
       <c r="B177" s="6" t="s">
-        <v>1679</v>
+        <v>1680</v>
       </c>
       <c r="C177" s="7" t="s">
-        <v>1680</v>
+        <v>1681</v>
       </c>
       <c r="D177" s="19"/>
       <c r="E177" s="3"/>
@@ -26348,10 +26353,10 @@
     <row r="178" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A178" s="5"/>
       <c r="B178" s="6" t="s">
-        <v>1681</v>
+        <v>1682</v>
       </c>
       <c r="C178" s="7" t="s">
-        <v>1682</v>
+        <v>1683</v>
       </c>
       <c r="D178" s="19"/>
       <c r="E178" s="3"/>
@@ -26359,10 +26364,10 @@
     <row r="179" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A179" s="5"/>
       <c r="B179" s="6" t="s">
-        <v>1683</v>
+        <v>1684</v>
       </c>
       <c r="C179" s="7" t="s">
-        <v>1684</v>
+        <v>1685</v>
       </c>
       <c r="D179" s="19"/>
       <c r="E179" s="3"/>
@@ -26370,10 +26375,10 @@
     <row r="180" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A180" s="5"/>
       <c r="B180" s="6" t="s">
-        <v>1685</v>
+        <v>1686</v>
       </c>
       <c r="C180" s="7" t="s">
-        <v>1686</v>
+        <v>1687</v>
       </c>
       <c r="D180" s="19"/>
       <c r="E180" s="3"/>
@@ -26381,10 +26386,10 @@
     <row r="181" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A181" s="5"/>
       <c r="B181" s="6" t="s">
-        <v>1687</v>
+        <v>1688</v>
       </c>
       <c r="C181" s="7" t="s">
-        <v>1688</v>
+        <v>1689</v>
       </c>
       <c r="D181" s="19"/>
       <c r="E181" s="3"/>
@@ -26392,10 +26397,10 @@
     <row r="182" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A182" s="5"/>
       <c r="B182" s="6" t="s">
-        <v>1689</v>
+        <v>1690</v>
       </c>
       <c r="C182" s="7" t="s">
-        <v>1690</v>
+        <v>1691</v>
       </c>
       <c r="D182" s="19"/>
       <c r="E182" s="3"/>
@@ -26403,10 +26408,10 @@
     <row r="183" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A183" s="5"/>
       <c r="B183" s="6" t="s">
-        <v>1691</v>
+        <v>1692</v>
       </c>
       <c r="C183" s="7" t="s">
-        <v>1692</v>
+        <v>1693</v>
       </c>
       <c r="D183" s="19"/>
       <c r="E183" s="3"/>
@@ -26414,10 +26419,10 @@
     <row r="184" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A184" s="5"/>
       <c r="B184" s="6" t="s">
-        <v>1693</v>
+        <v>1694</v>
       </c>
       <c r="C184" s="7" t="s">
-        <v>1694</v>
+        <v>1695</v>
       </c>
       <c r="D184" s="19"/>
       <c r="E184" s="3"/>
@@ -26425,10 +26430,10 @@
     <row r="185" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A185" s="5"/>
       <c r="B185" s="6" t="s">
-        <v>1695</v>
+        <v>1696</v>
       </c>
       <c r="C185" s="7" t="s">
-        <v>1696</v>
+        <v>1697</v>
       </c>
       <c r="D185" s="19"/>
       <c r="E185" s="3"/>
@@ -26436,10 +26441,10 @@
     <row r="186" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A186" s="5"/>
       <c r="B186" s="6" t="s">
-        <v>1697</v>
+        <v>1698</v>
       </c>
       <c r="C186" s="7" t="s">
-        <v>1698</v>
+        <v>1699</v>
       </c>
       <c r="D186" s="19"/>
       <c r="E186" s="3"/>
@@ -26447,10 +26452,10 @@
     <row r="187" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A187" s="5"/>
       <c r="B187" s="6" t="s">
-        <v>1699</v>
+        <v>1700</v>
       </c>
       <c r="C187" s="7" t="s">
-        <v>1700</v>
+        <v>1701</v>
       </c>
       <c r="D187" s="19"/>
       <c r="E187" s="3"/>
@@ -26458,10 +26463,10 @@
     <row r="188" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A188" s="5"/>
       <c r="B188" s="6" t="s">
-        <v>1701</v>
+        <v>1702</v>
       </c>
       <c r="C188" s="7" t="s">
-        <v>1702</v>
+        <v>1703</v>
       </c>
       <c r="D188" s="19"/>
       <c r="E188" s="3"/>
@@ -26469,10 +26474,10 @@
     <row r="189" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A189" s="5"/>
       <c r="B189" s="6" t="s">
-        <v>1703</v>
+        <v>1704</v>
       </c>
       <c r="C189" s="7" t="s">
-        <v>1704</v>
+        <v>1705</v>
       </c>
       <c r="D189" s="19"/>
       <c r="E189" s="3"/>
@@ -26480,10 +26485,10 @@
     <row r="190" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A190" s="5"/>
       <c r="B190" s="6" t="s">
-        <v>1705</v>
+        <v>1706</v>
       </c>
       <c r="C190" s="7" t="s">
-        <v>1706</v>
+        <v>1707</v>
       </c>
       <c r="D190" s="19"/>
       <c r="E190" s="3"/>
@@ -26491,10 +26496,10 @@
     <row r="191" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A191" s="5"/>
       <c r="B191" s="6" t="s">
-        <v>1707</v>
+        <v>1708</v>
       </c>
       <c r="C191" s="7" t="s">
-        <v>1708</v>
+        <v>1709</v>
       </c>
       <c r="D191" s="19"/>
       <c r="E191" s="3"/>
@@ -26502,10 +26507,10 @@
     <row r="192" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A192" s="5"/>
       <c r="B192" s="6" t="s">
-        <v>1709</v>
+        <v>1710</v>
       </c>
       <c r="C192" s="7" t="s">
-        <v>1710</v>
+        <v>1711</v>
       </c>
       <c r="D192" s="19"/>
       <c r="E192" s="3"/>
@@ -26513,10 +26518,10 @@
     <row r="193" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A193" s="5"/>
       <c r="B193" s="6" t="s">
-        <v>1711</v>
+        <v>1712</v>
       </c>
       <c r="C193" s="7" t="s">
-        <v>1712</v>
+        <v>1713</v>
       </c>
       <c r="D193" s="19"/>
       <c r="E193" s="3"/>
@@ -26524,10 +26529,10 @@
     <row r="194" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A194" s="5"/>
       <c r="B194" s="6" t="s">
-        <v>1713</v>
+        <v>1714</v>
       </c>
       <c r="C194" s="7" t="s">
-        <v>1714</v>
+        <v>1715</v>
       </c>
       <c r="D194" s="19"/>
       <c r="E194" s="3"/>
@@ -26535,10 +26540,10 @@
     <row r="195" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A195" s="5"/>
       <c r="B195" s="6" t="s">
-        <v>1715</v>
+        <v>1716</v>
       </c>
       <c r="C195" s="7" t="s">
-        <v>1716</v>
+        <v>1717</v>
       </c>
       <c r="D195" s="19"/>
       <c r="E195" s="3"/>
@@ -26546,10 +26551,10 @@
     <row r="196" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A196" s="5"/>
       <c r="B196" s="6" t="s">
-        <v>1717</v>
+        <v>1718</v>
       </c>
       <c r="C196" s="7" t="s">
-        <v>1718</v>
+        <v>1719</v>
       </c>
       <c r="D196" s="19"/>
       <c r="E196" s="3"/>
@@ -26557,10 +26562,10 @@
     <row r="197" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A197" s="5"/>
       <c r="B197" s="6" t="s">
-        <v>1719</v>
+        <v>1720</v>
       </c>
       <c r="C197" s="7" t="s">
-        <v>1720</v>
+        <v>1721</v>
       </c>
       <c r="D197" s="19"/>
       <c r="E197" s="3"/>
@@ -26568,10 +26573,10 @@
     <row r="198" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A198" s="5"/>
       <c r="B198" s="6" t="s">
-        <v>1721</v>
+        <v>1722</v>
       </c>
       <c r="C198" s="7" t="s">
-        <v>1722</v>
+        <v>1723</v>
       </c>
       <c r="D198" s="19"/>
       <c r="E198" s="3"/>
@@ -26579,10 +26584,10 @@
     <row r="199" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A199" s="5"/>
       <c r="B199" s="6" t="s">
-        <v>1723</v>
+        <v>1724</v>
       </c>
       <c r="C199" s="7" t="s">
-        <v>1724</v>
+        <v>1725</v>
       </c>
       <c r="D199" s="19"/>
       <c r="E199" s="3"/>
@@ -26590,10 +26595,10 @@
     <row r="200" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A200" s="5"/>
       <c r="B200" s="6" t="s">
-        <v>1725</v>
+        <v>1726</v>
       </c>
       <c r="C200" s="7" t="s">
-        <v>1726</v>
+        <v>1727</v>
       </c>
       <c r="D200" s="19"/>
       <c r="E200" s="3"/>
@@ -26601,10 +26606,10 @@
     <row r="201" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A201" s="5"/>
       <c r="B201" s="6" t="s">
-        <v>1727</v>
+        <v>1728</v>
       </c>
       <c r="C201" s="7" t="s">
-        <v>1728</v>
+        <v>1729</v>
       </c>
       <c r="D201" s="19"/>
       <c r="E201" s="3"/>
@@ -26612,10 +26617,10 @@
     <row r="202" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A202" s="5"/>
       <c r="B202" s="6" t="s">
-        <v>1729</v>
+        <v>1730</v>
       </c>
       <c r="C202" s="7" t="s">
-        <v>1730</v>
+        <v>1731</v>
       </c>
       <c r="D202" s="19"/>
       <c r="E202" s="3"/>
@@ -26623,10 +26628,10 @@
     <row r="203" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A203" s="5"/>
       <c r="B203" s="6" t="s">
-        <v>1731</v>
+        <v>1732</v>
       </c>
       <c r="C203" s="7" t="s">
-        <v>1732</v>
+        <v>1733</v>
       </c>
       <c r="D203" s="19"/>
       <c r="E203" s="3"/>
@@ -26634,10 +26639,10 @@
     <row r="204" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A204" s="5"/>
       <c r="B204" s="6" t="s">
-        <v>1733</v>
+        <v>1734</v>
       </c>
       <c r="C204" s="7" t="s">
-        <v>1734</v>
+        <v>1735</v>
       </c>
       <c r="D204" s="19"/>
       <c r="E204" s="3"/>
@@ -26645,10 +26650,10 @@
     <row r="205" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A205" s="5"/>
       <c r="B205" s="6" t="s">
-        <v>1735</v>
+        <v>1736</v>
       </c>
       <c r="C205" s="7" t="s">
-        <v>1736</v>
+        <v>1737</v>
       </c>
       <c r="D205" s="19"/>
       <c r="E205" s="3"/>
@@ -26656,10 +26661,10 @@
     <row r="206" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A206" s="5"/>
       <c r="B206" s="6" t="s">
-        <v>1737</v>
+        <v>1738</v>
       </c>
       <c r="C206" s="7" t="s">
-        <v>1738</v>
+        <v>1739</v>
       </c>
       <c r="D206" s="19"/>
       <c r="E206" s="3"/>
@@ -26667,10 +26672,10 @@
     <row r="207" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A207" s="5"/>
       <c r="B207" s="6" t="s">
-        <v>1739</v>
+        <v>1740</v>
       </c>
       <c r="C207" s="7" t="s">
-        <v>1740</v>
+        <v>1741</v>
       </c>
       <c r="D207" s="19"/>
       <c r="E207" s="3"/>
@@ -26678,10 +26683,10 @@
     <row r="208" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A208" s="5"/>
       <c r="B208" s="6" t="s">
-        <v>1741</v>
+        <v>1742</v>
       </c>
       <c r="C208" s="7" t="s">
-        <v>1742</v>
+        <v>1743</v>
       </c>
       <c r="D208" s="19"/>
       <c r="E208" s="3"/>
@@ -26689,10 +26694,10 @@
     <row r="209" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A209" s="5"/>
       <c r="B209" s="6" t="s">
-        <v>1743</v>
+        <v>1744</v>
       </c>
       <c r="C209" s="7" t="s">
-        <v>1744</v>
+        <v>1745</v>
       </c>
       <c r="D209" s="19"/>
       <c r="E209" s="3"/>
@@ -26700,10 +26705,10 @@
     <row r="210" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A210" s="5"/>
       <c r="B210" s="6" t="s">
-        <v>1745</v>
+        <v>1746</v>
       </c>
       <c r="C210" s="7" t="s">
-        <v>1746</v>
+        <v>1747</v>
       </c>
       <c r="D210" s="19"/>
       <c r="E210" s="3"/>
@@ -26711,10 +26716,10 @@
     <row r="211" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A211" s="5"/>
       <c r="B211" s="6" t="s">
-        <v>1747</v>
+        <v>1748</v>
       </c>
       <c r="C211" s="7" t="s">
-        <v>1748</v>
+        <v>1749</v>
       </c>
       <c r="D211" s="19"/>
       <c r="E211" s="3"/>
@@ -26722,10 +26727,10 @@
     <row r="212" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A212" s="5"/>
       <c r="B212" s="6" t="s">
-        <v>1749</v>
+        <v>1750</v>
       </c>
       <c r="C212" s="7" t="s">
-        <v>1750</v>
+        <v>1751</v>
       </c>
       <c r="D212" s="19"/>
       <c r="E212" s="3"/>
@@ -26733,10 +26738,10 @@
     <row r="213" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A213" s="5"/>
       <c r="B213" s="6" t="s">
-        <v>1751</v>
+        <v>1752</v>
       </c>
       <c r="C213" s="7" t="s">
-        <v>1752</v>
+        <v>1753</v>
       </c>
       <c r="D213" s="19"/>
       <c r="E213" s="3"/>
@@ -26744,10 +26749,10 @@
     <row r="214" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A214" s="5"/>
       <c r="B214" s="6" t="s">
-        <v>1753</v>
+        <v>1754</v>
       </c>
       <c r="C214" s="7" t="s">
-        <v>1754</v>
+        <v>1755</v>
       </c>
       <c r="D214" s="19"/>
       <c r="E214" s="3"/>
@@ -26755,10 +26760,10 @@
     <row r="215" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A215" s="5"/>
       <c r="B215" s="6" t="s">
-        <v>1755</v>
+        <v>1756</v>
       </c>
       <c r="C215" s="7" t="s">
-        <v>1756</v>
+        <v>1757</v>
       </c>
       <c r="D215" s="19"/>
       <c r="E215" s="3"/>
@@ -26766,10 +26771,10 @@
     <row r="216" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A216" s="5"/>
       <c r="B216" s="6" t="s">
-        <v>1757</v>
+        <v>1758</v>
       </c>
       <c r="C216" s="7" t="s">
-        <v>1758</v>
+        <v>1759</v>
       </c>
       <c r="D216" s="19"/>
       <c r="E216" s="3"/>
@@ -26777,10 +26782,10 @@
     <row r="217" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A217" s="5"/>
       <c r="B217" s="6" t="s">
-        <v>1759</v>
+        <v>1760</v>
       </c>
       <c r="C217" s="7" t="s">
-        <v>1760</v>
+        <v>1761</v>
       </c>
       <c r="D217" s="19"/>
       <c r="E217" s="3"/>
@@ -26788,10 +26793,10 @@
     <row r="218" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A218" s="5"/>
       <c r="B218" s="6" t="s">
-        <v>1761</v>
+        <v>1762</v>
       </c>
       <c r="C218" s="7" t="s">
-        <v>1762</v>
+        <v>1763</v>
       </c>
       <c r="D218" s="19"/>
       <c r="E218" s="3"/>
@@ -26799,10 +26804,10 @@
     <row r="219" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A219" s="5"/>
       <c r="B219" s="6" t="s">
-        <v>1763</v>
+        <v>1764</v>
       </c>
       <c r="C219" s="7" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="D219" s="19"/>
       <c r="E219" s="3"/>
@@ -26810,10 +26815,10 @@
     <row r="220" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A220" s="5"/>
       <c r="B220" s="6" t="s">
-        <v>1765</v>
+        <v>1766</v>
       </c>
       <c r="C220" s="7" t="s">
-        <v>1766</v>
+        <v>1767</v>
       </c>
       <c r="D220" s="19"/>
       <c r="E220" s="3"/>
@@ -26821,10 +26826,10 @@
     <row r="221" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A221" s="5"/>
       <c r="B221" s="6" t="s">
-        <v>1767</v>
+        <v>1768</v>
       </c>
       <c r="C221" s="7" t="s">
-        <v>1768</v>
+        <v>1769</v>
       </c>
       <c r="D221" s="19"/>
       <c r="E221" s="3"/>
@@ -26832,10 +26837,10 @@
     <row r="222" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A222" s="5"/>
       <c r="B222" s="6" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="C222" s="7" t="s">
-        <v>1770</v>
+        <v>1771</v>
       </c>
       <c r="D222" s="19"/>
       <c r="E222" s="3"/>
@@ -26843,10 +26848,10 @@
     <row r="223" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A223" s="5"/>
       <c r="B223" s="6" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="C223" s="7" t="s">
-        <v>1772</v>
+        <v>1773</v>
       </c>
       <c r="D223" s="19"/>
       <c r="E223" s="3"/>
@@ -26854,10 +26859,10 @@
     <row r="224" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A224" s="5"/>
       <c r="B224" s="6" t="s">
-        <v>1773</v>
+        <v>1774</v>
       </c>
       <c r="C224" s="7" t="s">
-        <v>1774</v>
+        <v>1775</v>
       </c>
       <c r="D224" s="19"/>
       <c r="E224" s="3"/>
@@ -26865,10 +26870,10 @@
     <row r="225" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A225" s="5"/>
       <c r="B225" s="6" t="s">
-        <v>1775</v>
+        <v>1776</v>
       </c>
       <c r="C225" s="7" t="s">
-        <v>1776</v>
+        <v>1777</v>
       </c>
       <c r="D225" s="19"/>
       <c r="E225" s="3"/>
@@ -26876,10 +26881,10 @@
     <row r="226" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A226" s="5"/>
       <c r="B226" s="6" t="s">
-        <v>1777</v>
+        <v>1778</v>
       </c>
       <c r="C226" s="7" t="s">
-        <v>1778</v>
+        <v>1779</v>
       </c>
       <c r="D226" s="19"/>
       <c r="E226" s="3"/>
@@ -26887,10 +26892,10 @@
     <row r="227" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A227" s="5"/>
       <c r="B227" s="6" t="s">
-        <v>1779</v>
+        <v>1780</v>
       </c>
       <c r="C227" s="7" t="s">
-        <v>1780</v>
+        <v>1781</v>
       </c>
       <c r="D227" s="19"/>
       <c r="E227" s="3"/>
@@ -26898,10 +26903,10 @@
     <row r="228" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A228" s="5"/>
       <c r="B228" s="6" t="s">
-        <v>1781</v>
+        <v>1782</v>
       </c>
       <c r="C228" s="7" t="s">
-        <v>1782</v>
+        <v>1783</v>
       </c>
       <c r="D228" s="19"/>
       <c r="E228" s="3"/>
@@ -26909,10 +26914,10 @@
     <row r="229" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A229" s="5"/>
       <c r="B229" s="6" t="s">
-        <v>1783</v>
+        <v>1784</v>
       </c>
       <c r="C229" s="7" t="s">
-        <v>1784</v>
+        <v>1785</v>
       </c>
       <c r="D229" s="19"/>
       <c r="E229" s="3"/>
@@ -26920,10 +26925,10 @@
     <row r="230" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A230" s="5"/>
       <c r="B230" s="6" t="s">
-        <v>1785</v>
+        <v>1786</v>
       </c>
       <c r="C230" s="7" t="s">
-        <v>1786</v>
+        <v>1787</v>
       </c>
       <c r="D230" s="19"/>
       <c r="E230" s="3"/>
@@ -26931,10 +26936,10 @@
     <row r="231" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A231" s="5"/>
       <c r="B231" s="6" t="s">
-        <v>1787</v>
+        <v>1788</v>
       </c>
       <c r="C231" s="7" t="s">
-        <v>1788</v>
+        <v>1789</v>
       </c>
       <c r="D231" s="19"/>
       <c r="E231" s="3"/>
@@ -26942,10 +26947,10 @@
     <row r="232" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A232" s="5"/>
       <c r="B232" s="6" t="s">
-        <v>1789</v>
+        <v>1790</v>
       </c>
       <c r="C232" s="7" t="s">
-        <v>1790</v>
+        <v>1791</v>
       </c>
       <c r="D232" s="19"/>
       <c r="E232" s="3"/>
@@ -26953,10 +26958,10 @@
     <row r="233" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A233" s="5"/>
       <c r="B233" s="6" t="s">
-        <v>1791</v>
+        <v>1792</v>
       </c>
       <c r="C233" s="7" t="s">
-        <v>1792</v>
+        <v>1793</v>
       </c>
       <c r="D233" s="19"/>
       <c r="E233" s="3"/>
@@ -26964,10 +26969,10 @@
     <row r="234" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A234" s="5"/>
       <c r="B234" s="6" t="s">
-        <v>1793</v>
+        <v>1794</v>
       </c>
       <c r="C234" s="7" t="s">
-        <v>1794</v>
+        <v>1795</v>
       </c>
       <c r="D234" s="19"/>
       <c r="E234" s="3"/>
@@ -26975,10 +26980,10 @@
     <row r="235" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A235" s="5"/>
       <c r="B235" s="6" t="s">
-        <v>1795</v>
+        <v>1796</v>
       </c>
       <c r="C235" s="7" t="s">
-        <v>1796</v>
+        <v>1797</v>
       </c>
       <c r="D235" s="19"/>
       <c r="E235" s="3"/>
@@ -26986,10 +26991,10 @@
     <row r="236" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A236" s="5"/>
       <c r="B236" s="6" t="s">
-        <v>1797</v>
+        <v>1798</v>
       </c>
       <c r="C236" s="7" t="s">
-        <v>1798</v>
+        <v>1799</v>
       </c>
       <c r="D236" s="19"/>
       <c r="E236" s="3"/>
@@ -26997,10 +27002,10 @@
     <row r="237" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A237" s="5"/>
       <c r="B237" s="6" t="s">
-        <v>1799</v>
+        <v>1800</v>
       </c>
       <c r="C237" s="7" t="s">
-        <v>1800</v>
+        <v>1801</v>
       </c>
       <c r="D237" s="19"/>
       <c r="E237" s="3"/>
@@ -27008,10 +27013,10 @@
     <row r="238" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A238" s="5"/>
       <c r="B238" s="6" t="s">
-        <v>1801</v>
+        <v>1802</v>
       </c>
       <c r="C238" s="7" t="s">
-        <v>1802</v>
+        <v>1803</v>
       </c>
       <c r="D238" s="19"/>
       <c r="E238" s="3"/>
@@ -27019,10 +27024,10 @@
     <row r="239" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A239" s="5"/>
       <c r="B239" s="6" t="s">
-        <v>1803</v>
+        <v>1804</v>
       </c>
       <c r="C239" s="7" t="s">
-        <v>1804</v>
+        <v>1805</v>
       </c>
       <c r="D239" s="19"/>
       <c r="E239" s="3"/>
@@ -27030,10 +27035,10 @@
     <row r="240" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A240" s="5"/>
       <c r="B240" s="6" t="s">
-        <v>1805</v>
+        <v>1806</v>
       </c>
       <c r="C240" s="7" t="s">
-        <v>1806</v>
+        <v>1807</v>
       </c>
       <c r="D240" s="19"/>
       <c r="E240" s="3"/>
@@ -27041,10 +27046,10 @@
     <row r="241" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A241" s="5"/>
       <c r="B241" s="6" t="s">
-        <v>1807</v>
+        <v>1808</v>
       </c>
       <c r="C241" s="7" t="s">
-        <v>1808</v>
+        <v>1809</v>
       </c>
       <c r="D241" s="19"/>
       <c r="E241" s="3"/>
@@ -27052,10 +27057,10 @@
     <row r="242" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A242" s="5"/>
       <c r="B242" s="6" t="s">
-        <v>1809</v>
+        <v>1810</v>
       </c>
       <c r="C242" s="7" t="s">
-        <v>1810</v>
+        <v>1811</v>
       </c>
       <c r="D242" s="19"/>
       <c r="E242" s="3"/>
@@ -27063,10 +27068,10 @@
     <row r="243" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A243" s="5"/>
       <c r="B243" s="6" t="s">
-        <v>1811</v>
+        <v>1812</v>
       </c>
       <c r="C243" s="7" t="s">
-        <v>1812</v>
+        <v>1813</v>
       </c>
       <c r="D243" s="19"/>
       <c r="E243" s="3"/>
@@ -27074,10 +27079,10 @@
     <row r="244" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A244" s="5"/>
       <c r="B244" s="6" t="s">
-        <v>1813</v>
+        <v>1814</v>
       </c>
       <c r="C244" s="7" t="s">
-        <v>1814</v>
+        <v>1815</v>
       </c>
       <c r="D244" s="19"/>
       <c r="E244" s="3"/>
@@ -27085,10 +27090,10 @@
     <row r="245" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A245" s="5"/>
       <c r="B245" s="6" t="s">
-        <v>1815</v>
+        <v>1816</v>
       </c>
       <c r="C245" s="7" t="s">
-        <v>1816</v>
+        <v>1817</v>
       </c>
       <c r="D245" s="19"/>
       <c r="E245" s="3"/>
@@ -27096,10 +27101,10 @@
     <row r="246" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A246" s="5"/>
       <c r="B246" s="6" t="s">
-        <v>1817</v>
+        <v>1818</v>
       </c>
       <c r="C246" s="7" t="s">
-        <v>1818</v>
+        <v>1819</v>
       </c>
       <c r="D246" s="19"/>
       <c r="E246" s="3"/>
@@ -27107,10 +27112,10 @@
     <row r="247" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A247" s="5"/>
       <c r="B247" s="6" t="s">
-        <v>1819</v>
+        <v>1820</v>
       </c>
       <c r="C247" s="7" t="s">
-        <v>1820</v>
+        <v>1821</v>
       </c>
       <c r="D247" s="19"/>
       <c r="E247" s="3"/>
@@ -27118,10 +27123,10 @@
     <row r="248" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A248" s="5"/>
       <c r="B248" s="6" t="s">
-        <v>1821</v>
+        <v>1822</v>
       </c>
       <c r="C248" s="7" t="s">
-        <v>1822</v>
+        <v>1823</v>
       </c>
       <c r="D248" s="19"/>
       <c r="E248" s="3"/>
@@ -27129,10 +27134,10 @@
     <row r="249" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A249" s="5"/>
       <c r="B249" s="6" t="s">
-        <v>1823</v>
+        <v>1824</v>
       </c>
       <c r="C249" s="7" t="s">
-        <v>1824</v>
+        <v>1825</v>
       </c>
       <c r="D249" s="19"/>
       <c r="E249" s="3"/>
@@ -27140,10 +27145,10 @@
     <row r="250" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A250" s="5"/>
       <c r="B250" s="11" t="s">
-        <v>1825</v>
+        <v>1826</v>
       </c>
       <c r="C250" s="12" t="s">
-        <v>1826</v>
+        <v>1827</v>
       </c>
       <c r="D250" s="19"/>
       <c r="E250" s="3"/>
@@ -27194,91 +27199,91 @@
     <row r="2" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A2" s="5"/>
       <c r="B2" s="6" t="s">
-        <v>1827</v>
+        <v>1828</v>
       </c>
       <c r="C2" s="7" t="s">
-        <v>1828</v>
+        <v>1829</v>
       </c>
       <c r="D2" s="21" t="s">
-        <v>1829</v>
+        <v>1830</v>
       </c>
       <c r="E2" s="3"/>
     </row>
     <row r="3" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A3" s="5"/>
       <c r="B3" s="6" t="s">
-        <v>1830</v>
+        <v>1831</v>
       </c>
       <c r="C3" s="7" t="s">
-        <v>1831</v>
+        <v>1832</v>
       </c>
       <c r="D3" s="21" t="s">
-        <v>1832</v>
+        <v>1833</v>
       </c>
       <c r="E3" s="3"/>
     </row>
     <row r="4" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="5"/>
       <c r="B4" s="6" t="s">
-        <v>1833</v>
+        <v>1834</v>
       </c>
       <c r="C4" s="7" t="s">
-        <v>1834</v>
+        <v>1835</v>
       </c>
       <c r="D4" s="21" t="s">
-        <v>1835</v>
+        <v>1836</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="5"/>
       <c r="B5" s="6" t="s">
-        <v>1836</v>
+        <v>1837</v>
       </c>
       <c r="C5" s="7" t="s">
-        <v>1837</v>
+        <v>1838</v>
       </c>
       <c r="D5" s="21" t="s">
-        <v>1838</v>
+        <v>1839</v>
       </c>
       <c r="E5" s="3"/>
     </row>
     <row r="6" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="5"/>
       <c r="B6" s="6" t="s">
-        <v>1839</v>
+        <v>1840</v>
       </c>
       <c r="C6" s="7" t="s">
-        <v>1840</v>
+        <v>1841</v>
       </c>
       <c r="D6" s="21" t="s">
-        <v>1841</v>
+        <v>1842</v>
       </c>
       <c r="E6" s="3"/>
     </row>
     <row r="7" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="5"/>
       <c r="B7" s="6" t="s">
-        <v>1842</v>
+        <v>1843</v>
       </c>
       <c r="C7" s="7" t="s">
-        <v>1843</v>
+        <v>1844</v>
       </c>
       <c r="D7" s="21" t="s">
-        <v>1844</v>
+        <v>1845</v>
       </c>
       <c r="E7" s="3"/>
     </row>
     <row r="8" customFormat="false" ht="13.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A8" s="5"/>
       <c r="B8" s="6" t="s">
-        <v>1845</v>
+        <v>1846</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>1846</v>
+        <v>1847</v>
       </c>
       <c r="D8" s="21" t="s">
-        <v>1847</v>
+        <v>1848</v>
       </c>
       <c r="E8" s="3"/>
     </row>
